--- a/Tools/Luban/DataTables/Datas/R_任务.xlsx
+++ b/Tools/Luban/DataTables/Datas/R_任务.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangwencheng/UnityProject/2025TTGJ/Tools/Luban/DataTables/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3976F916-48B8-4D41-8646-C178E891D7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B16072-86C3-F848-85B9-6F369AB9189A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="4920" windowWidth="23600" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -198,7 +198,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -206,7 +206,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -215,7 +215,7 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -224,7 +224,7 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF1F2329"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -232,14 +232,14 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -247,7 +247,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -418,7 +418,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -692,19 +692,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K181"/>
-  <sheetFormatPr defaultColWidth="12.08203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="12.08203125" style="1"/>
-    <col min="3" max="3" width="16.08203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.08203125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12.08203125" style="1"/>
-    <col min="7" max="9" width="24.08203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.4140625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="12" style="1"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="31.83203125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="12" style="1"/>
+    <col min="7" max="9" width="24" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="15.6640625" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="12.08203125" style="1"/>
+    <col min="12" max="16384" width="12" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -739,7 +739,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -753,7 +753,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>13</v>
@@ -774,7 +774,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
@@ -809,7 +809,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -844,7 +844,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B5" s="12">
         <v>1001</v>
       </c>
@@ -869,7 +869,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B6" s="12">
         <v>1002</v>
       </c>
@@ -901,7 +901,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="12">
         <v>1003</v>
@@ -934,7 +934,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
       <c r="B8" s="12">
         <v>1004</v>
@@ -954,7 +954,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="12">
         <v>1005</v>
@@ -987,7 +987,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
       <c r="B10" s="12">
         <v>1006</v>
@@ -1007,7 +1007,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
       <c r="B11" s="12">
         <v>1007</v>
@@ -1027,7 +1027,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
       <c r="B12" s="12">
         <v>1008</v>
@@ -1047,7 +1047,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
       <c r="B13" s="12">
         <v>1009</v>
@@ -1067,7 +1067,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="9"/>
       <c r="B14" s="12">
         <v>1010</v>
@@ -1087,1123 +1087,1123 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="10"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="9"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="10"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="10"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="10"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="10"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="10"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="10"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="10"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="10"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="10"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="10"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="10"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="10"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="10"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="10"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="10"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="10"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="10"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="10"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="10"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="10"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="10"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="10"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="10"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
       <c r="C49" s="10"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="10"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="10"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
       <c r="C52" s="10"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="9"/>
       <c r="B53" s="9"/>
       <c r="C53" s="10"/>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="10"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
       <c r="C55" s="10"/>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="10"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="9"/>
       <c r="B57" s="9"/>
       <c r="C57" s="10"/>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="9"/>
       <c r="B58" s="9"/>
       <c r="C58" s="10"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="9"/>
       <c r="B59" s="9"/>
       <c r="C59" s="10"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="9"/>
       <c r="B60" s="9"/>
       <c r="C60" s="10"/>
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="9"/>
       <c r="B61" s="9"/>
       <c r="C61" s="10"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="9"/>
       <c r="B62" s="9"/>
       <c r="C62" s="10"/>
       <c r="D62" s="9"/>
       <c r="E62" s="9"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="9"/>
       <c r="B63" s="9"/>
       <c r="C63" s="10"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="9"/>
       <c r="B64" s="9"/>
       <c r="C64" s="10"/>
       <c r="D64" s="9"/>
       <c r="E64" s="9"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="9"/>
       <c r="B65" s="9"/>
       <c r="C65" s="10"/>
       <c r="D65" s="9"/>
       <c r="E65" s="9"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="9"/>
       <c r="B66" s="9"/>
       <c r="C66" s="10"/>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="9"/>
       <c r="B67" s="9"/>
       <c r="C67" s="10"/>
       <c r="D67" s="9"/>
       <c r="E67" s="9"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="9"/>
       <c r="B68" s="9"/>
       <c r="C68" s="10"/>
       <c r="D68" s="9"/>
       <c r="E68" s="9"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="9"/>
       <c r="B69" s="9"/>
       <c r="C69" s="10"/>
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="9"/>
       <c r="B70" s="9"/>
       <c r="C70" s="10"/>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="9"/>
       <c r="B71" s="9"/>
       <c r="C71" s="10"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="9"/>
       <c r="B72" s="9"/>
       <c r="C72" s="10"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="9"/>
       <c r="B73" s="9"/>
       <c r="C73" s="10"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
       <c r="C74" s="10"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="9"/>
       <c r="B75" s="9"/>
       <c r="C75" s="10"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="9"/>
       <c r="B76" s="9"/>
       <c r="C76" s="10"/>
       <c r="D76" s="9"/>
       <c r="E76" s="9"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="9"/>
       <c r="B77" s="9"/>
       <c r="C77" s="10"/>
       <c r="D77" s="9"/>
       <c r="E77" s="9"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="9"/>
       <c r="B78" s="9"/>
       <c r="C78" s="10"/>
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="9"/>
       <c r="B79" s="9"/>
       <c r="C79" s="10"/>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="9"/>
       <c r="B80" s="9"/>
       <c r="C80" s="10"/>
       <c r="D80" s="9"/>
       <c r="E80" s="9"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="9"/>
       <c r="B81" s="9"/>
       <c r="C81" s="10"/>
       <c r="D81" s="9"/>
       <c r="E81" s="9"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="9"/>
       <c r="B82" s="9"/>
       <c r="C82" s="10"/>
       <c r="D82" s="9"/>
       <c r="E82" s="9"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="9"/>
       <c r="B83" s="9"/>
       <c r="C83" s="10"/>
       <c r="D83" s="9"/>
       <c r="E83" s="9"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="9"/>
       <c r="B84" s="9"/>
       <c r="C84" s="10"/>
       <c r="D84" s="9"/>
       <c r="E84" s="9"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="9"/>
       <c r="B85" s="9"/>
       <c r="C85" s="10"/>
       <c r="D85" s="9"/>
       <c r="E85" s="9"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="9"/>
       <c r="B86" s="9"/>
       <c r="C86" s="10"/>
       <c r="D86" s="9"/>
       <c r="E86" s="9"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="9"/>
       <c r="B87" s="9"/>
       <c r="C87" s="10"/>
       <c r="D87" s="9"/>
       <c r="E87" s="9"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="9"/>
       <c r="B88" s="9"/>
       <c r="C88" s="10"/>
       <c r="D88" s="9"/>
       <c r="E88" s="9"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="9"/>
       <c r="B89" s="9"/>
       <c r="C89" s="10"/>
       <c r="D89" s="9"/>
       <c r="E89" s="9"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="9"/>
       <c r="B90" s="9"/>
       <c r="C90" s="10"/>
       <c r="D90" s="9"/>
       <c r="E90" s="9"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="9"/>
       <c r="B91" s="9"/>
       <c r="C91" s="10"/>
       <c r="D91" s="9"/>
       <c r="E91" s="9"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="9"/>
       <c r="B92" s="9"/>
       <c r="C92" s="10"/>
       <c r="D92" s="9"/>
       <c r="E92" s="9"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="9"/>
       <c r="B93" s="9"/>
       <c r="C93" s="10"/>
       <c r="D93" s="9"/>
       <c r="E93" s="9"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="9"/>
       <c r="B94" s="9"/>
       <c r="C94" s="10"/>
       <c r="D94" s="9"/>
       <c r="E94" s="9"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="9"/>
       <c r="B95" s="9"/>
       <c r="C95" s="10"/>
       <c r="D95" s="9"/>
       <c r="E95" s="9"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="9"/>
       <c r="B96" s="9"/>
       <c r="C96" s="10"/>
       <c r="D96" s="9"/>
       <c r="E96" s="9"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="9"/>
       <c r="B97" s="9"/>
       <c r="C97" s="10"/>
       <c r="D97" s="9"/>
       <c r="E97" s="9"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="9"/>
       <c r="B98" s="9"/>
       <c r="C98" s="10"/>
       <c r="D98" s="9"/>
       <c r="E98" s="9"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="9"/>
       <c r="B99" s="9"/>
       <c r="C99" s="10"/>
       <c r="D99" s="9"/>
       <c r="E99" s="9"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="9"/>
       <c r="B100" s="9"/>
       <c r="C100" s="10"/>
       <c r="D100" s="9"/>
       <c r="E100" s="9"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="9"/>
       <c r="B101" s="9"/>
       <c r="C101" s="10"/>
       <c r="D101" s="9"/>
       <c r="E101" s="9"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="9"/>
       <c r="B102" s="9"/>
       <c r="C102" s="10"/>
       <c r="D102" s="9"/>
       <c r="E102" s="9"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="9"/>
       <c r="B103" s="9"/>
       <c r="C103" s="10"/>
       <c r="D103" s="9"/>
       <c r="E103" s="9"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="9"/>
       <c r="B104" s="9"/>
       <c r="C104" s="10"/>
       <c r="D104" s="9"/>
       <c r="E104" s="9"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="9"/>
       <c r="B105" s="9"/>
       <c r="C105" s="10"/>
       <c r="D105" s="9"/>
       <c r="E105" s="9"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="9"/>
       <c r="B106" s="9"/>
       <c r="C106" s="10"/>
       <c r="D106" s="9"/>
       <c r="E106" s="9"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="9"/>
       <c r="B107" s="9"/>
       <c r="C107" s="10"/>
       <c r="D107" s="9"/>
       <c r="E107" s="9"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="9"/>
       <c r="B108" s="9"/>
       <c r="C108" s="10"/>
       <c r="D108" s="9"/>
       <c r="E108" s="9"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="9"/>
       <c r="B109" s="9"/>
       <c r="C109" s="10"/>
       <c r="D109" s="9"/>
       <c r="E109" s="9"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="9"/>
       <c r="B110" s="9"/>
       <c r="C110" s="10"/>
       <c r="D110" s="9"/>
       <c r="E110" s="9"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="9"/>
       <c r="B111" s="9"/>
       <c r="C111" s="10"/>
       <c r="D111" s="9"/>
       <c r="E111" s="9"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" s="9"/>
       <c r="B112" s="9"/>
       <c r="C112" s="10"/>
       <c r="D112" s="9"/>
       <c r="E112" s="9"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="9"/>
       <c r="B113" s="9"/>
       <c r="C113" s="10"/>
       <c r="D113" s="9"/>
       <c r="E113" s="9"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="9"/>
       <c r="B114" s="9"/>
       <c r="C114" s="10"/>
       <c r="D114" s="9"/>
       <c r="E114" s="9"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="9"/>
       <c r="B115" s="9"/>
       <c r="C115" s="10"/>
       <c r="D115" s="9"/>
       <c r="E115" s="9"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="9"/>
       <c r="B116" s="9"/>
       <c r="C116" s="10"/>
       <c r="D116" s="9"/>
       <c r="E116" s="9"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="9"/>
       <c r="B117" s="9"/>
       <c r="C117" s="10"/>
       <c r="D117" s="9"/>
       <c r="E117" s="9"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="9"/>
       <c r="B118" s="9"/>
       <c r="C118" s="10"/>
       <c r="D118" s="9"/>
       <c r="E118" s="9"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" s="9"/>
       <c r="B119" s="9"/>
       <c r="C119" s="10"/>
       <c r="D119" s="9"/>
       <c r="E119" s="9"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" s="9"/>
       <c r="B120" s="9"/>
       <c r="C120" s="10"/>
       <c r="D120" s="9"/>
       <c r="E120" s="9"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="9"/>
       <c r="B121" s="9"/>
       <c r="C121" s="10"/>
       <c r="D121" s="9"/>
       <c r="E121" s="9"/>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" s="9"/>
       <c r="B122" s="9"/>
       <c r="C122" s="10"/>
       <c r="D122" s="9"/>
       <c r="E122" s="9"/>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="9"/>
       <c r="B123" s="9"/>
       <c r="C123" s="10"/>
       <c r="D123" s="9"/>
       <c r="E123" s="9"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="9"/>
       <c r="B124" s="9"/>
       <c r="C124" s="10"/>
       <c r="D124" s="9"/>
       <c r="E124" s="9"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="9"/>
       <c r="B125" s="9"/>
       <c r="C125" s="10"/>
       <c r="D125" s="9"/>
       <c r="E125" s="9"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="9"/>
       <c r="B126" s="9"/>
       <c r="C126" s="10"/>
       <c r="D126" s="9"/>
       <c r="E126" s="9"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="9"/>
       <c r="B127" s="9"/>
       <c r="C127" s="10"/>
       <c r="D127" s="9"/>
       <c r="E127" s="9"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="9"/>
       <c r="B128" s="9"/>
       <c r="C128" s="10"/>
       <c r="D128" s="9"/>
       <c r="E128" s="9"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="9"/>
       <c r="B129" s="9"/>
       <c r="C129" s="10"/>
       <c r="D129" s="9"/>
       <c r="E129" s="9"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="9"/>
       <c r="B130" s="9"/>
       <c r="C130" s="10"/>
       <c r="D130" s="9"/>
       <c r="E130" s="9"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="9"/>
       <c r="B131" s="9"/>
       <c r="C131" s="10"/>
       <c r="D131" s="9"/>
       <c r="E131" s="9"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="9"/>
       <c r="B132" s="9"/>
       <c r="C132" s="10"/>
       <c r="D132" s="9"/>
       <c r="E132" s="9"/>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="9"/>
       <c r="B133" s="9"/>
       <c r="C133" s="10"/>
       <c r="D133" s="9"/>
       <c r="E133" s="9"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="9"/>
       <c r="B134" s="9"/>
       <c r="C134" s="10"/>
       <c r="D134" s="9"/>
       <c r="E134" s="9"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="9"/>
       <c r="B135" s="9"/>
       <c r="C135" s="10"/>
       <c r="D135" s="9"/>
       <c r="E135" s="9"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="9"/>
       <c r="B136" s="9"/>
       <c r="C136" s="10"/>
       <c r="D136" s="9"/>
       <c r="E136" s="9"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="9"/>
       <c r="B137" s="9"/>
       <c r="C137" s="10"/>
       <c r="D137" s="9"/>
       <c r="E137" s="9"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="9"/>
       <c r="B138" s="9"/>
       <c r="C138" s="10"/>
       <c r="D138" s="9"/>
       <c r="E138" s="9"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" s="9"/>
       <c r="B139" s="9"/>
       <c r="C139" s="10"/>
       <c r="D139" s="9"/>
       <c r="E139" s="9"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" s="9"/>
       <c r="B140" s="9"/>
       <c r="C140" s="10"/>
       <c r="D140" s="9"/>
       <c r="E140" s="9"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="9"/>
       <c r="B141" s="9"/>
       <c r="C141" s="10"/>
       <c r="D141" s="9"/>
       <c r="E141" s="9"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="9"/>
       <c r="B142" s="9"/>
       <c r="C142" s="10"/>
       <c r="D142" s="9"/>
       <c r="E142" s="9"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" s="9"/>
       <c r="B143" s="9"/>
       <c r="C143" s="10"/>
       <c r="D143" s="9"/>
       <c r="E143" s="9"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="9"/>
       <c r="B144" s="9"/>
       <c r="C144" s="10"/>
       <c r="D144" s="9"/>
       <c r="E144" s="9"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="9"/>
       <c r="B145" s="9"/>
       <c r="C145" s="10"/>
       <c r="D145" s="9"/>
       <c r="E145" s="9"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="9"/>
       <c r="B146" s="9"/>
       <c r="C146" s="10"/>
       <c r="D146" s="9"/>
       <c r="E146" s="9"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="9"/>
       <c r="B147" s="9"/>
       <c r="C147" s="10"/>
       <c r="D147" s="9"/>
       <c r="E147" s="9"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="9"/>
       <c r="B148" s="9"/>
       <c r="C148" s="10"/>
       <c r="D148" s="9"/>
       <c r="E148" s="9"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="9"/>
       <c r="B149" s="9"/>
       <c r="C149" s="10"/>
       <c r="D149" s="9"/>
       <c r="E149" s="9"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" s="9"/>
       <c r="B150" s="9"/>
       <c r="C150" s="10"/>
       <c r="D150" s="9"/>
       <c r="E150" s="9"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="9"/>
       <c r="B151" s="9"/>
       <c r="C151" s="10"/>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="9"/>
       <c r="B152" s="9"/>
       <c r="C152" s="10"/>
       <c r="D152" s="9"/>
       <c r="E152" s="9"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="9"/>
       <c r="B153" s="9"/>
       <c r="C153" s="10"/>
       <c r="D153" s="9"/>
       <c r="E153" s="9"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="9"/>
       <c r="B154" s="9"/>
       <c r="C154" s="10"/>
       <c r="D154" s="9"/>
       <c r="E154" s="9"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="9"/>
       <c r="B155" s="9"/>
       <c r="C155" s="10"/>
       <c r="D155" s="9"/>
       <c r="E155" s="9"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" s="9"/>
       <c r="B156" s="9"/>
       <c r="C156" s="10"/>
       <c r="D156" s="9"/>
       <c r="E156" s="9"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="9"/>
       <c r="B157" s="9"/>
       <c r="C157" s="10"/>
       <c r="D157" s="9"/>
       <c r="E157" s="9"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="9"/>
       <c r="B158" s="9"/>
       <c r="C158" s="10"/>
       <c r="D158" s="9"/>
       <c r="E158" s="9"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="9"/>
       <c r="B159" s="9"/>
       <c r="C159" s="10"/>
       <c r="D159" s="9"/>
       <c r="E159" s="9"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="9"/>
       <c r="B160" s="9"/>
       <c r="C160" s="10"/>
       <c r="D160" s="9"/>
       <c r="E160" s="9"/>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="9"/>
       <c r="B161" s="9"/>
       <c r="C161" s="10"/>
       <c r="D161" s="9"/>
       <c r="E161" s="9"/>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="9"/>
       <c r="B162" s="9"/>
       <c r="C162" s="10"/>
       <c r="D162" s="9"/>
       <c r="E162" s="9"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" s="9"/>
       <c r="B163" s="9"/>
       <c r="C163" s="10"/>
       <c r="D163" s="9"/>
       <c r="E163" s="9"/>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="9"/>
       <c r="B164" s="9"/>
       <c r="C164" s="10"/>
       <c r="D164" s="9"/>
       <c r="E164" s="9"/>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="9"/>
       <c r="B165" s="9"/>
       <c r="C165" s="10"/>
       <c r="D165" s="9"/>
       <c r="E165" s="9"/>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="9"/>
       <c r="B166" s="9"/>
       <c r="C166" s="10"/>
       <c r="D166" s="9"/>
       <c r="E166" s="9"/>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="9"/>
       <c r="B167" s="9"/>
       <c r="C167" s="10"/>
       <c r="D167" s="9"/>
       <c r="E167" s="9"/>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="9"/>
       <c r="B168" s="9"/>
       <c r="C168" s="10"/>
       <c r="D168" s="9"/>
       <c r="E168" s="9"/>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="9"/>
       <c r="B169" s="9"/>
       <c r="C169" s="10"/>
       <c r="D169" s="9"/>
       <c r="E169" s="9"/>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="9"/>
       <c r="B170" s="9"/>
       <c r="C170" s="10"/>
       <c r="D170" s="9"/>
       <c r="E170" s="9"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" s="9"/>
       <c r="B171" s="9"/>
       <c r="C171" s="10"/>
       <c r="D171" s="9"/>
       <c r="E171" s="9"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="9"/>
       <c r="B172" s="9"/>
       <c r="C172" s="10"/>
       <c r="D172" s="9"/>
       <c r="E172" s="9"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="9"/>
       <c r="B173" s="9"/>
       <c r="C173" s="10"/>
       <c r="D173" s="9"/>
       <c r="E173" s="9"/>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="9"/>
       <c r="B174" s="9"/>
       <c r="C174" s="10"/>
       <c r="D174" s="9"/>
       <c r="E174" s="9"/>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="9"/>
       <c r="B175" s="9"/>
       <c r="C175" s="10"/>
       <c r="D175" s="9"/>
       <c r="E175" s="9"/>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="9"/>
       <c r="B176" s="9"/>
       <c r="C176" s="10"/>
       <c r="D176" s="9"/>
       <c r="E176" s="9"/>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="9"/>
       <c r="B177" s="9"/>
       <c r="C177" s="10"/>
       <c r="D177" s="9"/>
       <c r="E177" s="9"/>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="9"/>
       <c r="B178" s="9"/>
       <c r="C178" s="10"/>
       <c r="D178" s="9"/>
       <c r="E178" s="9"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="11"/>
       <c r="B179" s="11"/>
       <c r="C179" s="11"/>
       <c r="D179" s="11"/>
       <c r="E179" s="11"/>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="11"/>
       <c r="B180" s="11"/>
       <c r="C180" s="11"/>
       <c r="D180" s="11"/>
       <c r="E180" s="11"/>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="11"/>
       <c r="B181" s="11"/>
       <c r="C181" s="11"/>

--- a/Tools/Luban/DataTables/Datas/R_任务.xlsx
+++ b/Tools/Luban/DataTables/Datas/R_任务.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangwencheng/UnityProject/2025TTGJ/Tools/Luban/DataTables/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B16072-86C3-F848-85B9-6F369AB9189A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD3579F-AFF0-ED48-8B44-05FCA8791ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="4920" windowWidth="23600" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3160" yWindow="3620" windowWidth="23600" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
   <si>
     <t>##var</t>
   </si>
@@ -117,9 +117,6 @@
     <t>0甜菜 1羊 2猴子 3绿羊</t>
   </si>
   <si>
-    <t>道具id#数量</t>
-  </si>
-  <si>
     <t>接取时剧情&amp;接取时剧情</t>
   </si>
   <si>
@@ -138,37 +135,16 @@
     <t>初来乍到</t>
   </si>
   <si>
-    <t>1001#10&amp;5001#1</t>
-  </si>
-  <si>
     <t>种出十个土豆</t>
   </si>
   <si>
-    <t>2001#10</t>
-  </si>
-  <si>
-    <t>1013#1</t>
-  </si>
-  <si>
     <t>清理十个杂草</t>
   </si>
   <si>
-    <t>2016#10</t>
-  </si>
-  <si>
-    <t>1004#11</t>
-  </si>
-  <si>
     <t>新朋友</t>
   </si>
   <si>
     <t>新朋友程序猿</t>
-  </si>
-  <si>
-    <t>1004#1</t>
-  </si>
-  <si>
-    <t>1014#10</t>
   </si>
   <si>
     <t>奇怪的花椰菜</t>
@@ -188,13 +164,58 @@
   <si>
     <t>Art/Images/Icons/Group 62@2x#10</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=|),(ItemConfig#sep=,)</t>
+  </si>
+  <si>
+    <t>道具id,数量|道具id,数量</t>
+  </si>
+  <si>
+    <t>2001,10</t>
+  </si>
+  <si>
+    <t>2016,10</t>
+  </si>
+  <si>
+    <t>1004,1</t>
+  </si>
+  <si>
+    <t>1001,10|5001,1</t>
+  </si>
+  <si>
+    <t>1013,1</t>
+  </si>
+  <si>
+    <t>1004,11</t>
+  </si>
+  <si>
+    <t>1014,10</t>
+  </si>
+  <si>
+    <t>201,202</t>
+  </si>
+  <si>
+    <t>208,209</t>
+  </si>
+  <si>
+    <t>214,215,216</t>
+  </si>
+  <si>
+    <t>203,204</t>
+  </si>
+  <si>
+    <t>211,212,213</t>
+  </si>
+  <si>
+    <t>218,219</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,8 +273,29 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,6 +311,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -375,7 +423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -395,12 +443,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -415,6 +457,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -697,7 +754,8 @@
     <col min="1" max="2" width="12" style="1"/>
     <col min="3" max="3" width="16" style="1" customWidth="1"/>
     <col min="4" max="4" width="31.83203125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12" style="1"/>
+    <col min="5" max="5" width="39.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="33.33203125" style="1" customWidth="1"/>
     <col min="7" max="9" width="24" style="1" customWidth="1"/>
     <col min="10" max="10" width="17.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="15.6640625" style="1" customWidth="1"/>
@@ -739,7 +797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -752,11 +810,11 @@
       <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>13</v>
+      <c r="E2" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>14</v>
@@ -822,178 +880,178 @@
       <c r="D4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="J4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="K4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B5" s="10">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="12">
-        <v>1001</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="D5" s="6">
         <v>0</v>
       </c>
       <c r="E5" s="6"/>
-      <c r="F5" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="7">
-        <v>201202</v>
-      </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="7">
-        <v>203204</v>
-      </c>
-      <c r="J5" s="12">
+      <c r="F5" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="15"/>
+      <c r="I5" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="10">
         <v>1002</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="12">
+      <c r="B6" s="10">
         <v>1002</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D6" s="6">
         <v>0</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="8">
+      <c r="E6" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="15">
         <v>205</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="15">
         <v>206</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="15">
         <v>207</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="10">
         <v>1003</v>
       </c>
-      <c r="K6" s="13" t="s">
-        <v>51</v>
+      <c r="K6" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="9"/>
-      <c r="B7" s="12">
+      <c r="A7" s="7"/>
+      <c r="B7" s="10">
         <v>1003</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D7" s="6">
         <v>0</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="7">
-        <v>208209</v>
-      </c>
-      <c r="H7" s="8">
+      <c r="E7" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="15">
         <v>210</v>
       </c>
-      <c r="I7" s="7">
-        <v>211212213</v>
-      </c>
-      <c r="J7" s="12">
+      <c r="I7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" s="10">
         <v>1004</v>
       </c>
-      <c r="K7" s="13" t="s">
-        <v>51</v>
+      <c r="K7" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="9"/>
-      <c r="B8" s="12">
+      <c r="A8" s="7"/>
+      <c r="B8" s="10">
         <v>1004</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D8" s="6">
         <v>0</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="12">
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="10">
         <v>1005</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="9"/>
-      <c r="B9" s="12">
+      <c r="A9" s="7"/>
+      <c r="B9" s="10">
         <v>1005</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D9" s="6">
         <v>2</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="7">
-        <v>214215216</v>
-      </c>
-      <c r="H9" s="8">
+      <c r="E9" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="15">
         <v>217</v>
       </c>
-      <c r="I9" s="7">
-        <v>218219</v>
-      </c>
-      <c r="J9" s="12">
+      <c r="I9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" s="10">
         <v>1006</v>
       </c>
-      <c r="K9" s="13" t="s">
-        <v>51</v>
+      <c r="K9" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="9"/>
-      <c r="B10" s="12">
+      <c r="A10" s="7"/>
+      <c r="B10" s="10">
         <v>1006</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D10" s="6">
         <v>2</v>
@@ -1003,17 +1061,17 @@
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
-      <c r="J10" s="12">
+      <c r="J10" s="10">
         <v>1007</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="9"/>
-      <c r="B11" s="12">
+      <c r="A11" s="7"/>
+      <c r="B11" s="10">
         <v>1007</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D11" s="6">
         <v>1</v>
@@ -1023,17 +1081,17 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
-      <c r="J11" s="12">
+      <c r="J11" s="10">
         <v>1008</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="9"/>
-      <c r="B12" s="12">
+      <c r="A12" s="7"/>
+      <c r="B12" s="10">
         <v>1008</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D12" s="6">
         <v>2</v>
@@ -1043,17 +1101,17 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
-      <c r="J12" s="12">
+      <c r="J12" s="10">
         <v>1009</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="9"/>
-      <c r="B13" s="12">
+      <c r="A13" s="7"/>
+      <c r="B13" s="10">
         <v>1009</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D13" s="6">
         <v>3</v>
@@ -1063,17 +1121,17 @@
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
-      <c r="J13" s="12">
+      <c r="J13" s="10">
         <v>1010</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="9"/>
-      <c r="B14" s="12">
+      <c r="A14" s="7"/>
+      <c r="B14" s="10">
         <v>1010</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D14" s="6">
         <v>4</v>
@@ -1083,1132 +1141,1133 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
-      <c r="J14" s="12">
+      <c r="J14" s="10">
         <v>1011</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="9"/>
+      <c r="A18" s="7"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="9"/>
+      <c r="A19" s="7"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="9"/>
+      <c r="A20" s="7"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="9"/>
+      <c r="A21" s="7"/>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="9"/>
+      <c r="A22" s="7"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="9"/>
+      <c r="A23" s="7"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="9"/>
+      <c r="A24" s="7"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="9"/>
+      <c r="A25" s="7"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
+      <c r="A52" s="7"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="9"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="10"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="9"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
+      <c r="A56" s="7"/>
+      <c r="B56" s="7"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="9"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" s="9"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="10"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="9"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
+      <c r="A59" s="7"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="9"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
+      <c r="A60" s="7"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" s="9"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="10"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
+      <c r="A61" s="7"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="9"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="10"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
+      <c r="A62" s="7"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" s="9"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="10"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
+      <c r="A63" s="7"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" s="9"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
+      <c r="A64" s="7"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" s="9"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
+      <c r="A65" s="7"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" s="9"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="10"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
+      <c r="A66" s="7"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" s="9"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="10"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
+      <c r="A67" s="7"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" s="9"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
+      <c r="A68" s="7"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" s="9"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="10"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
+      <c r="A69" s="7"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" s="9"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="10"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
+      <c r="A70" s="7"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" s="9"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="10"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
+      <c r="A71" s="7"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" s="9"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
+      <c r="A72" s="7"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73" s="9"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="10"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
+      <c r="A73" s="7"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" s="9"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="10"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
+      <c r="A74" s="7"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" s="9"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="10"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" s="9"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
+      <c r="A76" s="7"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" s="9"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="10"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" s="9"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="10"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
+      <c r="A78" s="7"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" s="9"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="10"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
+      <c r="A79" s="7"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80" s="9"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
+      <c r="A80" s="7"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81" s="9"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="10"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
+      <c r="A81" s="7"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="9"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="10"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
+      <c r="A82" s="7"/>
+      <c r="B82" s="7"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83" s="9"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="10"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
+      <c r="A83" s="7"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="9"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
+      <c r="A84" s="7"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" s="9"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="10"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
+      <c r="A85" s="7"/>
+      <c r="B85" s="7"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" s="9"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="10"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="9"/>
+      <c r="A86" s="7"/>
+      <c r="B86" s="7"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A87" s="9"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="10"/>
-      <c r="D87" s="9"/>
-      <c r="E87" s="9"/>
+      <c r="A87" s="7"/>
+      <c r="B87" s="7"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A88" s="9"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
+      <c r="A88" s="7"/>
+      <c r="B88" s="7"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A89" s="9"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="10"/>
-      <c r="D89" s="9"/>
-      <c r="E89" s="9"/>
+      <c r="A89" s="7"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90" s="9"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="10"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
+      <c r="A90" s="7"/>
+      <c r="B90" s="7"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="7"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A91" s="9"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="10"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="9"/>
+      <c r="A91" s="7"/>
+      <c r="B91" s="7"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A92" s="9"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="9"/>
+      <c r="A92" s="7"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A93" s="9"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="10"/>
-      <c r="D93" s="9"/>
-      <c r="E93" s="9"/>
+      <c r="A93" s="7"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A94" s="9"/>
-      <c r="B94" s="9"/>
-      <c r="C94" s="10"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="9"/>
+      <c r="A94" s="7"/>
+      <c r="B94" s="7"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="7"/>
+      <c r="E94" s="7"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A95" s="9"/>
-      <c r="B95" s="9"/>
-      <c r="C95" s="10"/>
-      <c r="D95" s="9"/>
-      <c r="E95" s="9"/>
+      <c r="A95" s="7"/>
+      <c r="B95" s="7"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A96" s="9"/>
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="9"/>
-      <c r="E96" s="9"/>
+      <c r="A96" s="7"/>
+      <c r="B96" s="7"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="7"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A97" s="9"/>
-      <c r="B97" s="9"/>
-      <c r="C97" s="10"/>
-      <c r="D97" s="9"/>
-      <c r="E97" s="9"/>
+      <c r="A97" s="7"/>
+      <c r="B97" s="7"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A98" s="9"/>
-      <c r="B98" s="9"/>
-      <c r="C98" s="10"/>
-      <c r="D98" s="9"/>
-      <c r="E98" s="9"/>
+      <c r="A98" s="7"/>
+      <c r="B98" s="7"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="7"/>
+      <c r="E98" s="7"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A99" s="9"/>
-      <c r="B99" s="9"/>
-      <c r="C99" s="10"/>
-      <c r="D99" s="9"/>
-      <c r="E99" s="9"/>
+      <c r="A99" s="7"/>
+      <c r="B99" s="7"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A100" s="9"/>
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="9"/>
-      <c r="E100" s="9"/>
+      <c r="A100" s="7"/>
+      <c r="B100" s="7"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="7"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A101" s="9"/>
-      <c r="B101" s="9"/>
-      <c r="C101" s="10"/>
-      <c r="D101" s="9"/>
-      <c r="E101" s="9"/>
+      <c r="A101" s="7"/>
+      <c r="B101" s="7"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A102" s="9"/>
-      <c r="B102" s="9"/>
-      <c r="C102" s="10"/>
-      <c r="D102" s="9"/>
-      <c r="E102" s="9"/>
+      <c r="A102" s="7"/>
+      <c r="B102" s="7"/>
+      <c r="C102" s="8"/>
+      <c r="D102" s="7"/>
+      <c r="E102" s="7"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A103" s="9"/>
-      <c r="B103" s="9"/>
-      <c r="C103" s="10"/>
-      <c r="D103" s="9"/>
-      <c r="E103" s="9"/>
+      <c r="A103" s="7"/>
+      <c r="B103" s="7"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="7"/>
+      <c r="E103" s="7"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A104" s="9"/>
-      <c r="B104" s="9"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="9"/>
-      <c r="E104" s="9"/>
+      <c r="A104" s="7"/>
+      <c r="B104" s="7"/>
+      <c r="C104" s="8"/>
+      <c r="D104" s="7"/>
+      <c r="E104" s="7"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A105" s="9"/>
-      <c r="B105" s="9"/>
-      <c r="C105" s="10"/>
-      <c r="D105" s="9"/>
-      <c r="E105" s="9"/>
+      <c r="A105" s="7"/>
+      <c r="B105" s="7"/>
+      <c r="C105" s="8"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="7"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A106" s="9"/>
-      <c r="B106" s="9"/>
-      <c r="C106" s="10"/>
-      <c r="D106" s="9"/>
-      <c r="E106" s="9"/>
+      <c r="A106" s="7"/>
+      <c r="B106" s="7"/>
+      <c r="C106" s="8"/>
+      <c r="D106" s="7"/>
+      <c r="E106" s="7"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A107" s="9"/>
-      <c r="B107" s="9"/>
-      <c r="C107" s="10"/>
-      <c r="D107" s="9"/>
-      <c r="E107" s="9"/>
+      <c r="A107" s="7"/>
+      <c r="B107" s="7"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="7"/>
+      <c r="E107" s="7"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A108" s="9"/>
-      <c r="B108" s="9"/>
-      <c r="C108" s="10"/>
-      <c r="D108" s="9"/>
-      <c r="E108" s="9"/>
+      <c r="A108" s="7"/>
+      <c r="B108" s="7"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="7"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A109" s="9"/>
-      <c r="B109" s="9"/>
-      <c r="C109" s="10"/>
-      <c r="D109" s="9"/>
-      <c r="E109" s="9"/>
+      <c r="A109" s="7"/>
+      <c r="B109" s="7"/>
+      <c r="C109" s="8"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="7"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A110" s="9"/>
-      <c r="B110" s="9"/>
-      <c r="C110" s="10"/>
-      <c r="D110" s="9"/>
-      <c r="E110" s="9"/>
+      <c r="A110" s="7"/>
+      <c r="B110" s="7"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="7"/>
+      <c r="E110" s="7"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A111" s="9"/>
-      <c r="B111" s="9"/>
-      <c r="C111" s="10"/>
-      <c r="D111" s="9"/>
-      <c r="E111" s="9"/>
+      <c r="A111" s="7"/>
+      <c r="B111" s="7"/>
+      <c r="C111" s="8"/>
+      <c r="D111" s="7"/>
+      <c r="E111" s="7"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A112" s="9"/>
-      <c r="B112" s="9"/>
-      <c r="C112" s="10"/>
-      <c r="D112" s="9"/>
-      <c r="E112" s="9"/>
+      <c r="A112" s="7"/>
+      <c r="B112" s="7"/>
+      <c r="C112" s="8"/>
+      <c r="D112" s="7"/>
+      <c r="E112" s="7"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A113" s="9"/>
-      <c r="B113" s="9"/>
-      <c r="C113" s="10"/>
-      <c r="D113" s="9"/>
-      <c r="E113" s="9"/>
+      <c r="A113" s="7"/>
+      <c r="B113" s="7"/>
+      <c r="C113" s="8"/>
+      <c r="D113" s="7"/>
+      <c r="E113" s="7"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A114" s="9"/>
-      <c r="B114" s="9"/>
-      <c r="C114" s="10"/>
-      <c r="D114" s="9"/>
-      <c r="E114" s="9"/>
+      <c r="A114" s="7"/>
+      <c r="B114" s="7"/>
+      <c r="C114" s="8"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="7"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A115" s="9"/>
-      <c r="B115" s="9"/>
-      <c r="C115" s="10"/>
-      <c r="D115" s="9"/>
-      <c r="E115" s="9"/>
+      <c r="A115" s="7"/>
+      <c r="B115" s="7"/>
+      <c r="C115" s="8"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="7"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A116" s="9"/>
-      <c r="B116" s="9"/>
-      <c r="C116" s="10"/>
-      <c r="D116" s="9"/>
-      <c r="E116" s="9"/>
+      <c r="A116" s="7"/>
+      <c r="B116" s="7"/>
+      <c r="C116" s="8"/>
+      <c r="D116" s="7"/>
+      <c r="E116" s="7"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A117" s="9"/>
-      <c r="B117" s="9"/>
-      <c r="C117" s="10"/>
-      <c r="D117" s="9"/>
-      <c r="E117" s="9"/>
+      <c r="A117" s="7"/>
+      <c r="B117" s="7"/>
+      <c r="C117" s="8"/>
+      <c r="D117" s="7"/>
+      <c r="E117" s="7"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A118" s="9"/>
-      <c r="B118" s="9"/>
-      <c r="C118" s="10"/>
-      <c r="D118" s="9"/>
-      <c r="E118" s="9"/>
+      <c r="A118" s="7"/>
+      <c r="B118" s="7"/>
+      <c r="C118" s="8"/>
+      <c r="D118" s="7"/>
+      <c r="E118" s="7"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A119" s="9"/>
-      <c r="B119" s="9"/>
-      <c r="C119" s="10"/>
-      <c r="D119" s="9"/>
-      <c r="E119" s="9"/>
+      <c r="A119" s="7"/>
+      <c r="B119" s="7"/>
+      <c r="C119" s="8"/>
+      <c r="D119" s="7"/>
+      <c r="E119" s="7"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A120" s="9"/>
-      <c r="B120" s="9"/>
-      <c r="C120" s="10"/>
-      <c r="D120" s="9"/>
-      <c r="E120" s="9"/>
+      <c r="A120" s="7"/>
+      <c r="B120" s="7"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="7"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A121" s="9"/>
-      <c r="B121" s="9"/>
-      <c r="C121" s="10"/>
-      <c r="D121" s="9"/>
-      <c r="E121" s="9"/>
+      <c r="A121" s="7"/>
+      <c r="B121" s="7"/>
+      <c r="C121" s="8"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A122" s="9"/>
-      <c r="B122" s="9"/>
-      <c r="C122" s="10"/>
-      <c r="D122" s="9"/>
-      <c r="E122" s="9"/>
+      <c r="A122" s="7"/>
+      <c r="B122" s="7"/>
+      <c r="C122" s="8"/>
+      <c r="D122" s="7"/>
+      <c r="E122" s="7"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A123" s="9"/>
-      <c r="B123" s="9"/>
-      <c r="C123" s="10"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="9"/>
+      <c r="A123" s="7"/>
+      <c r="B123" s="7"/>
+      <c r="C123" s="8"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A124" s="9"/>
-      <c r="B124" s="9"/>
-      <c r="C124" s="10"/>
-      <c r="D124" s="9"/>
-      <c r="E124" s="9"/>
+      <c r="A124" s="7"/>
+      <c r="B124" s="7"/>
+      <c r="C124" s="8"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="7"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A125" s="9"/>
-      <c r="B125" s="9"/>
-      <c r="C125" s="10"/>
-      <c r="D125" s="9"/>
-      <c r="E125" s="9"/>
+      <c r="A125" s="7"/>
+      <c r="B125" s="7"/>
+      <c r="C125" s="8"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="7"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A126" s="9"/>
-      <c r="B126" s="9"/>
-      <c r="C126" s="10"/>
-      <c r="D126" s="9"/>
-      <c r="E126" s="9"/>
+      <c r="A126" s="7"/>
+      <c r="B126" s="7"/>
+      <c r="C126" s="8"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="7"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A127" s="9"/>
-      <c r="B127" s="9"/>
-      <c r="C127" s="10"/>
-      <c r="D127" s="9"/>
-      <c r="E127" s="9"/>
+      <c r="A127" s="7"/>
+      <c r="B127" s="7"/>
+      <c r="C127" s="8"/>
+      <c r="D127" s="7"/>
+      <c r="E127" s="7"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A128" s="9"/>
-      <c r="B128" s="9"/>
-      <c r="C128" s="10"/>
-      <c r="D128" s="9"/>
-      <c r="E128" s="9"/>
+      <c r="A128" s="7"/>
+      <c r="B128" s="7"/>
+      <c r="C128" s="8"/>
+      <c r="D128" s="7"/>
+      <c r="E128" s="7"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A129" s="9"/>
-      <c r="B129" s="9"/>
-      <c r="C129" s="10"/>
-      <c r="D129" s="9"/>
-      <c r="E129" s="9"/>
+      <c r="A129" s="7"/>
+      <c r="B129" s="7"/>
+      <c r="C129" s="8"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="7"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A130" s="9"/>
-      <c r="B130" s="9"/>
-      <c r="C130" s="10"/>
-      <c r="D130" s="9"/>
-      <c r="E130" s="9"/>
+      <c r="A130" s="7"/>
+      <c r="B130" s="7"/>
+      <c r="C130" s="8"/>
+      <c r="D130" s="7"/>
+      <c r="E130" s="7"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A131" s="9"/>
-      <c r="B131" s="9"/>
-      <c r="C131" s="10"/>
-      <c r="D131" s="9"/>
-      <c r="E131" s="9"/>
+      <c r="A131" s="7"/>
+      <c r="B131" s="7"/>
+      <c r="C131" s="8"/>
+      <c r="D131" s="7"/>
+      <c r="E131" s="7"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A132" s="9"/>
-      <c r="B132" s="9"/>
-      <c r="C132" s="10"/>
-      <c r="D132" s="9"/>
-      <c r="E132" s="9"/>
+      <c r="A132" s="7"/>
+      <c r="B132" s="7"/>
+      <c r="C132" s="8"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="7"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A133" s="9"/>
-      <c r="B133" s="9"/>
-      <c r="C133" s="10"/>
-      <c r="D133" s="9"/>
-      <c r="E133" s="9"/>
+      <c r="A133" s="7"/>
+      <c r="B133" s="7"/>
+      <c r="C133" s="8"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="7"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A134" s="9"/>
-      <c r="B134" s="9"/>
-      <c r="C134" s="10"/>
-      <c r="D134" s="9"/>
-      <c r="E134" s="9"/>
+      <c r="A134" s="7"/>
+      <c r="B134" s="7"/>
+      <c r="C134" s="8"/>
+      <c r="D134" s="7"/>
+      <c r="E134" s="7"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A135" s="9"/>
-      <c r="B135" s="9"/>
-      <c r="C135" s="10"/>
-      <c r="D135" s="9"/>
-      <c r="E135" s="9"/>
+      <c r="A135" s="7"/>
+      <c r="B135" s="7"/>
+      <c r="C135" s="8"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A136" s="9"/>
-      <c r="B136" s="9"/>
-      <c r="C136" s="10"/>
-      <c r="D136" s="9"/>
-      <c r="E136" s="9"/>
+      <c r="A136" s="7"/>
+      <c r="B136" s="7"/>
+      <c r="C136" s="8"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A137" s="9"/>
-      <c r="B137" s="9"/>
-      <c r="C137" s="10"/>
-      <c r="D137" s="9"/>
-      <c r="E137" s="9"/>
+      <c r="A137" s="7"/>
+      <c r="B137" s="7"/>
+      <c r="C137" s="8"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="7"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A138" s="9"/>
-      <c r="B138" s="9"/>
-      <c r="C138" s="10"/>
-      <c r="D138" s="9"/>
-      <c r="E138" s="9"/>
+      <c r="A138" s="7"/>
+      <c r="B138" s="7"/>
+      <c r="C138" s="8"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="7"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A139" s="9"/>
-      <c r="B139" s="9"/>
-      <c r="C139" s="10"/>
-      <c r="D139" s="9"/>
-      <c r="E139" s="9"/>
+      <c r="A139" s="7"/>
+      <c r="B139" s="7"/>
+      <c r="C139" s="8"/>
+      <c r="D139" s="7"/>
+      <c r="E139" s="7"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A140" s="9"/>
-      <c r="B140" s="9"/>
-      <c r="C140" s="10"/>
-      <c r="D140" s="9"/>
-      <c r="E140" s="9"/>
+      <c r="A140" s="7"/>
+      <c r="B140" s="7"/>
+      <c r="C140" s="8"/>
+      <c r="D140" s="7"/>
+      <c r="E140" s="7"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A141" s="9"/>
-      <c r="B141" s="9"/>
-      <c r="C141" s="10"/>
-      <c r="D141" s="9"/>
-      <c r="E141" s="9"/>
+      <c r="A141" s="7"/>
+      <c r="B141" s="7"/>
+      <c r="C141" s="8"/>
+      <c r="D141" s="7"/>
+      <c r="E141" s="7"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A142" s="9"/>
-      <c r="B142" s="9"/>
-      <c r="C142" s="10"/>
-      <c r="D142" s="9"/>
-      <c r="E142" s="9"/>
+      <c r="A142" s="7"/>
+      <c r="B142" s="7"/>
+      <c r="C142" s="8"/>
+      <c r="D142" s="7"/>
+      <c r="E142" s="7"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A143" s="9"/>
-      <c r="B143" s="9"/>
-      <c r="C143" s="10"/>
-      <c r="D143" s="9"/>
-      <c r="E143" s="9"/>
+      <c r="A143" s="7"/>
+      <c r="B143" s="7"/>
+      <c r="C143" s="8"/>
+      <c r="D143" s="7"/>
+      <c r="E143" s="7"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A144" s="9"/>
-      <c r="B144" s="9"/>
-      <c r="C144" s="10"/>
-      <c r="D144" s="9"/>
-      <c r="E144" s="9"/>
+      <c r="A144" s="7"/>
+      <c r="B144" s="7"/>
+      <c r="C144" s="8"/>
+      <c r="D144" s="7"/>
+      <c r="E144" s="7"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A145" s="9"/>
-      <c r="B145" s="9"/>
-      <c r="C145" s="10"/>
-      <c r="D145" s="9"/>
-      <c r="E145" s="9"/>
+      <c r="A145" s="7"/>
+      <c r="B145" s="7"/>
+      <c r="C145" s="8"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A146" s="9"/>
-      <c r="B146" s="9"/>
-      <c r="C146" s="10"/>
-      <c r="D146" s="9"/>
-      <c r="E146" s="9"/>
+      <c r="A146" s="7"/>
+      <c r="B146" s="7"/>
+      <c r="C146" s="8"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="7"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A147" s="9"/>
-      <c r="B147" s="9"/>
-      <c r="C147" s="10"/>
-      <c r="D147" s="9"/>
-      <c r="E147" s="9"/>
+      <c r="A147" s="7"/>
+      <c r="B147" s="7"/>
+      <c r="C147" s="8"/>
+      <c r="D147" s="7"/>
+      <c r="E147" s="7"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A148" s="9"/>
-      <c r="B148" s="9"/>
-      <c r="C148" s="10"/>
-      <c r="D148" s="9"/>
-      <c r="E148" s="9"/>
+      <c r="A148" s="7"/>
+      <c r="B148" s="7"/>
+      <c r="C148" s="8"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A149" s="9"/>
-      <c r="B149" s="9"/>
-      <c r="C149" s="10"/>
-      <c r="D149" s="9"/>
-      <c r="E149" s="9"/>
+      <c r="A149" s="7"/>
+      <c r="B149" s="7"/>
+      <c r="C149" s="8"/>
+      <c r="D149" s="7"/>
+      <c r="E149" s="7"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A150" s="9"/>
-      <c r="B150" s="9"/>
-      <c r="C150" s="10"/>
-      <c r="D150" s="9"/>
-      <c r="E150" s="9"/>
+      <c r="A150" s="7"/>
+      <c r="B150" s="7"/>
+      <c r="C150" s="8"/>
+      <c r="D150" s="7"/>
+      <c r="E150" s="7"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A151" s="9"/>
-      <c r="B151" s="9"/>
-      <c r="C151" s="10"/>
-      <c r="D151" s="9"/>
-      <c r="E151" s="9"/>
+      <c r="A151" s="7"/>
+      <c r="B151" s="7"/>
+      <c r="C151" s="8"/>
+      <c r="D151" s="7"/>
+      <c r="E151" s="7"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A152" s="9"/>
-      <c r="B152" s="9"/>
-      <c r="C152" s="10"/>
-      <c r="D152" s="9"/>
-      <c r="E152" s="9"/>
+      <c r="A152" s="7"/>
+      <c r="B152" s="7"/>
+      <c r="C152" s="8"/>
+      <c r="D152" s="7"/>
+      <c r="E152" s="7"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A153" s="9"/>
-      <c r="B153" s="9"/>
-      <c r="C153" s="10"/>
-      <c r="D153" s="9"/>
-      <c r="E153" s="9"/>
+      <c r="A153" s="7"/>
+      <c r="B153" s="7"/>
+      <c r="C153" s="8"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A154" s="9"/>
-      <c r="B154" s="9"/>
-      <c r="C154" s="10"/>
-      <c r="D154" s="9"/>
-      <c r="E154" s="9"/>
+      <c r="A154" s="7"/>
+      <c r="B154" s="7"/>
+      <c r="C154" s="8"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="7"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A155" s="9"/>
-      <c r="B155" s="9"/>
-      <c r="C155" s="10"/>
-      <c r="D155" s="9"/>
-      <c r="E155" s="9"/>
+      <c r="A155" s="7"/>
+      <c r="B155" s="7"/>
+      <c r="C155" s="8"/>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A156" s="9"/>
-      <c r="B156" s="9"/>
-      <c r="C156" s="10"/>
-      <c r="D156" s="9"/>
-      <c r="E156" s="9"/>
+      <c r="A156" s="7"/>
+      <c r="B156" s="7"/>
+      <c r="C156" s="8"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A157" s="9"/>
-      <c r="B157" s="9"/>
-      <c r="C157" s="10"/>
-      <c r="D157" s="9"/>
-      <c r="E157" s="9"/>
+      <c r="A157" s="7"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="8"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A158" s="9"/>
-      <c r="B158" s="9"/>
-      <c r="C158" s="10"/>
-      <c r="D158" s="9"/>
-      <c r="E158" s="9"/>
+      <c r="A158" s="7"/>
+      <c r="B158" s="7"/>
+      <c r="C158" s="8"/>
+      <c r="D158" s="7"/>
+      <c r="E158" s="7"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A159" s="9"/>
-      <c r="B159" s="9"/>
-      <c r="C159" s="10"/>
-      <c r="D159" s="9"/>
-      <c r="E159" s="9"/>
+      <c r="A159" s="7"/>
+      <c r="B159" s="7"/>
+      <c r="C159" s="8"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A160" s="9"/>
-      <c r="B160" s="9"/>
-      <c r="C160" s="10"/>
-      <c r="D160" s="9"/>
-      <c r="E160" s="9"/>
+      <c r="A160" s="7"/>
+      <c r="B160" s="7"/>
+      <c r="C160" s="8"/>
+      <c r="D160" s="7"/>
+      <c r="E160" s="7"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A161" s="9"/>
-      <c r="B161" s="9"/>
-      <c r="C161" s="10"/>
-      <c r="D161" s="9"/>
-      <c r="E161" s="9"/>
+      <c r="A161" s="7"/>
+      <c r="B161" s="7"/>
+      <c r="C161" s="8"/>
+      <c r="D161" s="7"/>
+      <c r="E161" s="7"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A162" s="9"/>
-      <c r="B162" s="9"/>
-      <c r="C162" s="10"/>
-      <c r="D162" s="9"/>
-      <c r="E162" s="9"/>
+      <c r="A162" s="7"/>
+      <c r="B162" s="7"/>
+      <c r="C162" s="8"/>
+      <c r="D162" s="7"/>
+      <c r="E162" s="7"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A163" s="9"/>
-      <c r="B163" s="9"/>
-      <c r="C163" s="10"/>
-      <c r="D163" s="9"/>
-      <c r="E163" s="9"/>
+      <c r="A163" s="7"/>
+      <c r="B163" s="7"/>
+      <c r="C163" s="8"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A164" s="9"/>
-      <c r="B164" s="9"/>
-      <c r="C164" s="10"/>
-      <c r="D164" s="9"/>
-      <c r="E164" s="9"/>
+      <c r="A164" s="7"/>
+      <c r="B164" s="7"/>
+      <c r="C164" s="8"/>
+      <c r="D164" s="7"/>
+      <c r="E164" s="7"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A165" s="9"/>
-      <c r="B165" s="9"/>
-      <c r="C165" s="10"/>
-      <c r="D165" s="9"/>
-      <c r="E165" s="9"/>
+      <c r="A165" s="7"/>
+      <c r="B165" s="7"/>
+      <c r="C165" s="8"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A166" s="9"/>
-      <c r="B166" s="9"/>
-      <c r="C166" s="10"/>
-      <c r="D166" s="9"/>
-      <c r="E166" s="9"/>
+      <c r="A166" s="7"/>
+      <c r="B166" s="7"/>
+      <c r="C166" s="8"/>
+      <c r="D166" s="7"/>
+      <c r="E166" s="7"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A167" s="9"/>
-      <c r="B167" s="9"/>
-      <c r="C167" s="10"/>
-      <c r="D167" s="9"/>
-      <c r="E167" s="9"/>
+      <c r="A167" s="7"/>
+      <c r="B167" s="7"/>
+      <c r="C167" s="8"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="7"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A168" s="9"/>
-      <c r="B168" s="9"/>
-      <c r="C168" s="10"/>
-      <c r="D168" s="9"/>
-      <c r="E168" s="9"/>
+      <c r="A168" s="7"/>
+      <c r="B168" s="7"/>
+      <c r="C168" s="8"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="7"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A169" s="9"/>
-      <c r="B169" s="9"/>
-      <c r="C169" s="10"/>
-      <c r="D169" s="9"/>
-      <c r="E169" s="9"/>
+      <c r="A169" s="7"/>
+      <c r="B169" s="7"/>
+      <c r="C169" s="8"/>
+      <c r="D169" s="7"/>
+      <c r="E169" s="7"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A170" s="9"/>
-      <c r="B170" s="9"/>
-      <c r="C170" s="10"/>
-      <c r="D170" s="9"/>
-      <c r="E170" s="9"/>
+      <c r="A170" s="7"/>
+      <c r="B170" s="7"/>
+      <c r="C170" s="8"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="7"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A171" s="9"/>
-      <c r="B171" s="9"/>
-      <c r="C171" s="10"/>
-      <c r="D171" s="9"/>
-      <c r="E171" s="9"/>
+      <c r="A171" s="7"/>
+      <c r="B171" s="7"/>
+      <c r="C171" s="8"/>
+      <c r="D171" s="7"/>
+      <c r="E171" s="7"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A172" s="9"/>
-      <c r="B172" s="9"/>
-      <c r="C172" s="10"/>
-      <c r="D172" s="9"/>
-      <c r="E172" s="9"/>
+      <c r="A172" s="7"/>
+      <c r="B172" s="7"/>
+      <c r="C172" s="8"/>
+      <c r="D172" s="7"/>
+      <c r="E172" s="7"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A173" s="9"/>
-      <c r="B173" s="9"/>
-      <c r="C173" s="10"/>
-      <c r="D173" s="9"/>
-      <c r="E173" s="9"/>
+      <c r="A173" s="7"/>
+      <c r="B173" s="7"/>
+      <c r="C173" s="8"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="7"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A174" s="9"/>
-      <c r="B174" s="9"/>
-      <c r="C174" s="10"/>
-      <c r="D174" s="9"/>
-      <c r="E174" s="9"/>
+      <c r="A174" s="7"/>
+      <c r="B174" s="7"/>
+      <c r="C174" s="8"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="7"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A175" s="9"/>
-      <c r="B175" s="9"/>
-      <c r="C175" s="10"/>
-      <c r="D175" s="9"/>
-      <c r="E175" s="9"/>
+      <c r="A175" s="7"/>
+      <c r="B175" s="7"/>
+      <c r="C175" s="8"/>
+      <c r="D175" s="7"/>
+      <c r="E175" s="7"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A176" s="9"/>
-      <c r="B176" s="9"/>
-      <c r="C176" s="10"/>
-      <c r="D176" s="9"/>
-      <c r="E176" s="9"/>
+      <c r="A176" s="7"/>
+      <c r="B176" s="7"/>
+      <c r="C176" s="8"/>
+      <c r="D176" s="7"/>
+      <c r="E176" s="7"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A177" s="9"/>
-      <c r="B177" s="9"/>
-      <c r="C177" s="10"/>
-      <c r="D177" s="9"/>
-      <c r="E177" s="9"/>
+      <c r="A177" s="7"/>
+      <c r="B177" s="7"/>
+      <c r="C177" s="8"/>
+      <c r="D177" s="7"/>
+      <c r="E177" s="7"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A178" s="9"/>
-      <c r="B178" s="9"/>
-      <c r="C178" s="10"/>
-      <c r="D178" s="9"/>
-      <c r="E178" s="9"/>
+      <c r="A178" s="7"/>
+      <c r="B178" s="7"/>
+      <c r="C178" s="8"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="7"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A179" s="11"/>
-      <c r="B179" s="11"/>
-      <c r="C179" s="11"/>
-      <c r="D179" s="11"/>
-      <c r="E179" s="11"/>
+      <c r="A179" s="9"/>
+      <c r="B179" s="9"/>
+      <c r="C179" s="9"/>
+      <c r="D179" s="9"/>
+      <c r="E179" s="9"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A180" s="11"/>
-      <c r="B180" s="11"/>
-      <c r="C180" s="11"/>
-      <c r="D180" s="11"/>
-      <c r="E180" s="11"/>
+      <c r="A180" s="9"/>
+      <c r="B180" s="9"/>
+      <c r="C180" s="9"/>
+      <c r="D180" s="9"/>
+      <c r="E180" s="9"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A181" s="11"/>
-      <c r="B181" s="11"/>
-      <c r="C181" s="11"/>
-      <c r="D181" s="11"/>
-      <c r="E181" s="11"/>
+      <c r="A181" s="9"/>
+      <c r="B181" s="9"/>
+      <c r="C181" s="9"/>
+      <c r="D181" s="9"/>
+      <c r="E181" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/Tools/Luban/DataTables/Datas/R_任务.xlsx
+++ b/Tools/Luban/DataTables/Datas/R_任务.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18360"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="119">
   <si>
     <t>##var</t>
   </si>
@@ -137,7 +137,7 @@
     <t>初来乍到</t>
   </si>
   <si>
-    <t>1001,10|5001,1</t>
+    <t>1001,1|5001,1</t>
   </si>
   <si>
     <t>201,202</t>
@@ -146,64 +146,244 @@
     <t>203,204</t>
   </si>
   <si>
-    <t>种出十个土豆</t>
-  </si>
-  <si>
-    <t>2001,1</t>
+    <t>种植土豆</t>
+  </si>
+  <si>
+    <t>2001,10</t>
   </si>
   <si>
     <t>1013,1</t>
   </si>
   <si>
-    <t>Art/Images/Icons/Group 62@2x#10</t>
-  </si>
-  <si>
-    <t>清理十个杂草</t>
+    <t>207,208</t>
+  </si>
+  <si>
+    <t>img/Potato</t>
+  </si>
+  <si>
+    <t>清理杂草</t>
   </si>
   <si>
     <t>2016,10</t>
   </si>
   <si>
-    <t>1004,11</t>
-  </si>
-  <si>
-    <t>208,209</t>
-  </si>
-  <si>
-    <t>211,212,213</t>
-  </si>
-  <si>
-    <t>新朋友</t>
-  </si>
-  <si>
-    <t>新朋友程序猿</t>
-  </si>
-  <si>
-    <t>1004,1</t>
-  </si>
-  <si>
-    <t>1014,10</t>
-  </si>
-  <si>
-    <t>214,215,216</t>
+    <t>1002,1</t>
+  </si>
+  <si>
+    <t>209,210</t>
+  </si>
+  <si>
+    <t>img/Yecao</t>
+  </si>
+  <si>
+    <t>种植蘑菇</t>
+  </si>
+  <si>
+    <t>2002,10</t>
+  </si>
+  <si>
+    <t>1005,1</t>
+  </si>
+  <si>
+    <t>213,214,215,216</t>
   </si>
   <si>
     <t>218,219</t>
   </si>
   <si>
-    <t>奇怪的花椰菜</t>
+    <t>img/Mushroom</t>
   </si>
   <si>
     <t>爆米花机</t>
   </si>
   <si>
-    <t>蔬菜房子</t>
-  </si>
-  <si>
-    <t>七色番茄</t>
+    <t>1006,1</t>
+  </si>
+  <si>
+    <t>220,221</t>
+  </si>
+  <si>
+    <t>222,223</t>
+  </si>
+  <si>
+    <t>送东西</t>
+  </si>
+  <si>
+    <t>5007,1</t>
+  </si>
+  <si>
+    <t>225,226,227</t>
+  </si>
+  <si>
+    <t>228,229,230</t>
+  </si>
+  <si>
+    <t>231,232</t>
+  </si>
+  <si>
+    <t>红番茄</t>
+  </si>
+  <si>
+    <t>2006,1</t>
+  </si>
+  <si>
+    <t>1014,1|5045,1</t>
+  </si>
+  <si>
+    <t>234,235,236,237</t>
+  </si>
+  <si>
+    <t>238,239,240,241</t>
+  </si>
+  <si>
+    <t>img/Tomato_Red</t>
+  </si>
+  <si>
+    <t>花椰菜</t>
+  </si>
+  <si>
+    <t>2013,10</t>
+  </si>
+  <si>
+    <t>1003,1</t>
+  </si>
+  <si>
+    <t>242,243,244,245</t>
+  </si>
+  <si>
+    <t>246,247</t>
+  </si>
+  <si>
+    <t>248,249,250,251</t>
+  </si>
+  <si>
+    <t>img/CauliFlower</t>
+  </si>
+  <si>
+    <t>南瓜</t>
+  </si>
+  <si>
+    <t>2003,1</t>
+  </si>
+  <si>
+    <t>5045,1</t>
+  </si>
+  <si>
+    <t>252,253,254</t>
+  </si>
+  <si>
+    <t>255,256,257</t>
+  </si>
+  <si>
+    <t>258,259,260,261,262</t>
+  </si>
+  <si>
+    <t>img/Pumpkin</t>
+  </si>
+  <si>
+    <t>橙番茄</t>
+  </si>
+  <si>
+    <t>1007,1</t>
+  </si>
+  <si>
+    <t>263,264,265</t>
+  </si>
+  <si>
+    <t>266,267</t>
+  </si>
+  <si>
+    <t>img/Tomato_Orange</t>
+  </si>
+  <si>
+    <t>黄番茄</t>
+  </si>
+  <si>
+    <t>1008,1</t>
+  </si>
+  <si>
+    <t>270,271,272</t>
+  </si>
+  <si>
+    <t>img/Tomato_Yellow</t>
+  </si>
+  <si>
+    <t>绿番茄</t>
+  </si>
+  <si>
+    <t>1009,1</t>
+  </si>
+  <si>
+    <t>273,274</t>
+  </si>
+  <si>
+    <t>275,276,277,278</t>
+  </si>
+  <si>
+    <t>279,280,281</t>
+  </si>
+  <si>
+    <t>img/Tomato_Green</t>
+  </si>
+  <si>
+    <t>青番茄</t>
+  </si>
+  <si>
+    <t>1010,1</t>
+  </si>
+  <si>
+    <t>282,283,284</t>
+  </si>
+  <si>
+    <t>285,286</t>
+  </si>
+  <si>
+    <t>287,288</t>
+  </si>
+  <si>
+    <t>img/Tomato_Cyan</t>
+  </si>
+  <si>
+    <t>蓝番茄</t>
+  </si>
+  <si>
+    <t>1011,1</t>
+  </si>
+  <si>
+    <t>289,290,291</t>
+  </si>
+  <si>
+    <t>img/Tomato_Blue</t>
+  </si>
+  <si>
+    <t>紫番茄</t>
+  </si>
+  <si>
+    <t>1012,1</t>
+  </si>
+  <si>
+    <t>294,295</t>
+  </si>
+  <si>
+    <t>296,297,298</t>
+  </si>
+  <si>
+    <t>img/Tomato_Purple</t>
   </si>
   <si>
     <t>999土豆</t>
+  </si>
+  <si>
+    <t>1001,999</t>
+  </si>
+  <si>
+    <t>299,301,302,303</t>
+  </si>
+  <si>
+    <t>304,305,306</t>
+  </si>
+  <si>
+    <t>307,308</t>
   </si>
 </sst>
 </file>
@@ -216,7 +396,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,7 +440,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -272,13 +451,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -428,7 +600,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -588,12 +760,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -854,151 +1020,163 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1007,14 +1185,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1022,13 +1206,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1351,1525 +1541,1761 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K181"/>
-  <sheetFormatPr defaultColWidth="12" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="12" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="12" style="1"/>
     <col min="3" max="3" width="16" style="1" customWidth="1"/>
     <col min="4" max="4" width="31.8333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="33.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="9" width="24" style="1" customWidth="1"/>
+    <col min="5" max="5" width="39.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="33.3333333333333" style="2" customWidth="1"/>
+    <col min="7" max="7" width="29.5583333333333" style="3" customWidth="1"/>
+    <col min="8" max="9" width="24" style="3" customWidth="1"/>
     <col min="10" max="10" width="17.3333333333333" style="1" customWidth="1"/>
     <col min="11" max="11" width="15.6666666666667" style="1" customWidth="1"/>
     <col min="12" max="16384" width="12" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="11" t="s">
         <v>33</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
-      <c r="B5" s="7">
+    <row r="5" spans="1:11">
+      <c r="B5" s="11">
         <v>1001</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="11">
         <v>0</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8" t="s">
+      <c r="E5" s="14"/>
+      <c r="F5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="9" t="s">
+      <c r="H5" s="15"/>
+      <c r="I5" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="11">
         <v>1002</v>
       </c>
     </row>
-    <row r="6" spans="2:11">
-      <c r="B6" s="7">
+    <row r="6" spans="1:11">
+      <c r="B6" s="11">
         <v>1002</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="11">
         <v>0</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="15">
         <v>205</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="15">
         <v>206</v>
       </c>
-      <c r="I6" s="10">
-        <v>207</v>
-      </c>
-      <c r="J6" s="7">
+      <c r="I6" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="11">
         <v>1003</v>
       </c>
-      <c r="K6" s="14" t="s">
-        <v>42</v>
+      <c r="K6" s="16" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="11"/>
-      <c r="B7" s="7">
+      <c r="A7" s="17"/>
+      <c r="B7" s="11">
         <v>1003</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="15">
+        <v>211</v>
+      </c>
+      <c r="I7" s="15">
+        <v>212</v>
+      </c>
+      <c r="J7" s="11">
+        <v>1004</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="17"/>
+      <c r="B8" s="11">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="15">
+        <v>217</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="11">
+        <v>1005</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="17"/>
+      <c r="B9" s="11">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="11">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="15">
+        <v>224</v>
+      </c>
+      <c r="J9" s="11">
+        <v>1006</v>
+      </c>
+      <c r="K9" s="16"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="17"/>
+      <c r="B10" s="11">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" s="11">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="17"/>
+      <c r="B11" s="11">
+        <v>1007</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="11">
+        <v>2</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="11">
+        <v>1008</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="17"/>
+      <c r="B12" s="11">
+        <v>1008</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" s="11">
+        <v>1009</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="17"/>
+      <c r="B13" s="11">
+        <v>1009</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="11">
+        <v>2</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" s="11">
+        <v>1010</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="17"/>
+      <c r="B14" s="11">
+        <v>1010</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="11">
+        <v>2</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="J14" s="11">
+        <v>1011</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17">
+        <v>1011</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="17">
+        <v>2</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="15">
+        <v>269</v>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1012</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="1">
+        <v>1012</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1013</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="B17" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1014</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="17"/>
+      <c r="B18" s="1">
+        <v>1014</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="H18" s="20">
+        <v>292</v>
+      </c>
+      <c r="I18" s="20">
+        <v>293</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1015</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="17"/>
+      <c r="B19" s="1">
+        <v>1015</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1016</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="17"/>
+      <c r="B20" s="1">
+        <v>1016</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="7">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="10">
-        <v>210</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" s="7">
-        <v>1004</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="11"/>
-      <c r="B8" s="7">
-        <v>1004</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="7">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="7">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="11"/>
-      <c r="B9" s="7">
-        <v>1005</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="7">
-        <v>2</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="10">
-        <v>217</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="7">
-        <v>1006</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="11"/>
-      <c r="B10" s="7">
-        <v>1006</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="7">
-        <v>2</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="11"/>
-      <c r="B11" s="7">
-        <v>1007</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="11"/>
-      <c r="B12" s="7">
-        <v>1008</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="7">
-        <v>2</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="11"/>
-      <c r="B13" s="7">
-        <v>1009</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="7">
-        <v>3</v>
-      </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="11"/>
-      <c r="B14" s="7">
-        <v>1010</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="7">
-        <v>4</v>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="11"/>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="11"/>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="11"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="11"/>
-      <c r="E21" s="13"/>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="11"/>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="11"/>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="11"/>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="11"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="17"/>
+      <c r="E21" s="21"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="17"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="17"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="17"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="17"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="19"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="19"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="19"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="19"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="19"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="19"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="19"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="19"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="19"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="19"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="19"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="19"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="19"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="19"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="19"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="19"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="11"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="19"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="11"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="19"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="11"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="19"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="11"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="19"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="11"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="19"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="11"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="19"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="11"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="19"/>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="11"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="19"/>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="11"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="19"/>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="11"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
+      <c r="A51" s="17"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="19"/>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="11"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
+      <c r="A52" s="17"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="19"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="11"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="19"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="11"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="19"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="11"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="19"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="11"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="19"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
+      <c r="A57" s="17"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="19"/>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="11"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
+      <c r="A58" s="17"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="19"/>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="11"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
+      <c r="A59" s="17"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="19"/>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="11"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="19"/>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="11"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
+      <c r="A61" s="17"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="19"/>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="11"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
+      <c r="A62" s="17"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="19"/>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="11"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
+      <c r="A63" s="17"/>
+      <c r="B63" s="17"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="19"/>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="11"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="11"/>
+      <c r="A64" s="17"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="19"/>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
+      <c r="A65" s="17"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="19"/>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="11"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
+      <c r="A66" s="17"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="19"/>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="11"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="19"/>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="11"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
+      <c r="A68" s="17"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="19"/>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="11"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
+      <c r="A69" s="17"/>
+      <c r="B69" s="17"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="19"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="11"/>
-      <c r="B70" s="11"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
+      <c r="A70" s="17"/>
+      <c r="B70" s="17"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="17"/>
+      <c r="E70" s="19"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="11"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
+      <c r="A71" s="17"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="19"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="11"/>
-      <c r="B72" s="11"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
+      <c r="A72" s="17"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="17"/>
+      <c r="E72" s="19"/>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="11"/>
-      <c r="B73" s="11"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
+      <c r="A73" s="17"/>
+      <c r="B73" s="17"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="17"/>
+      <c r="E73" s="19"/>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="11"/>
-      <c r="B74" s="11"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
+      <c r="A74" s="17"/>
+      <c r="B74" s="17"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="17"/>
+      <c r="E74" s="19"/>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="11"/>
-      <c r="B75" s="11"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
+      <c r="A75" s="17"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="17"/>
+      <c r="E75" s="19"/>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="11"/>
-      <c r="B76" s="11"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
+      <c r="A76" s="17"/>
+      <c r="B76" s="17"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="17"/>
+      <c r="E76" s="19"/>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="11"/>
-      <c r="B77" s="11"/>
-      <c r="C77" s="12"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
+      <c r="A77" s="17"/>
+      <c r="B77" s="17"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="17"/>
+      <c r="E77" s="19"/>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="11"/>
-      <c r="B78" s="11"/>
-      <c r="C78" s="12"/>
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
+      <c r="A78" s="17"/>
+      <c r="B78" s="17"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="17"/>
+      <c r="E78" s="19"/>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="11"/>
-      <c r="B79" s="11"/>
-      <c r="C79" s="12"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
+      <c r="A79" s="17"/>
+      <c r="B79" s="17"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="17"/>
+      <c r="E79" s="19"/>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="11"/>
-      <c r="B80" s="11"/>
-      <c r="C80" s="12"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
+      <c r="A80" s="17"/>
+      <c r="B80" s="17"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="17"/>
+      <c r="E80" s="19"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="11"/>
-      <c r="B81" s="11"/>
-      <c r="C81" s="12"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
+      <c r="A81" s="17"/>
+      <c r="B81" s="17"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="19"/>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="11"/>
-      <c r="B82" s="11"/>
-      <c r="C82" s="12"/>
-      <c r="D82" s="11"/>
-      <c r="E82" s="11"/>
+      <c r="A82" s="17"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="17"/>
+      <c r="E82" s="19"/>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="11"/>
-      <c r="B83" s="11"/>
-      <c r="C83" s="12"/>
-      <c r="D83" s="11"/>
-      <c r="E83" s="11"/>
+      <c r="A83" s="17"/>
+      <c r="B83" s="17"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="17"/>
+      <c r="E83" s="19"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="11"/>
-      <c r="B84" s="11"/>
-      <c r="C84" s="12"/>
-      <c r="D84" s="11"/>
-      <c r="E84" s="11"/>
+      <c r="A84" s="17"/>
+      <c r="B84" s="17"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="17"/>
+      <c r="E84" s="19"/>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="11"/>
-      <c r="B85" s="11"/>
-      <c r="C85" s="12"/>
-      <c r="D85" s="11"/>
-      <c r="E85" s="11"/>
+      <c r="A85" s="17"/>
+      <c r="B85" s="17"/>
+      <c r="C85" s="18"/>
+      <c r="D85" s="17"/>
+      <c r="E85" s="19"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="11"/>
-      <c r="B86" s="11"/>
-      <c r="C86" s="12"/>
-      <c r="D86" s="11"/>
-      <c r="E86" s="11"/>
+      <c r="A86" s="17"/>
+      <c r="B86" s="17"/>
+      <c r="C86" s="18"/>
+      <c r="D86" s="17"/>
+      <c r="E86" s="19"/>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="11"/>
-      <c r="B87" s="11"/>
-      <c r="C87" s="12"/>
-      <c r="D87" s="11"/>
-      <c r="E87" s="11"/>
+      <c r="A87" s="17"/>
+      <c r="B87" s="17"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="17"/>
+      <c r="E87" s="19"/>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="11"/>
-      <c r="B88" s="11"/>
-      <c r="C88" s="12"/>
-      <c r="D88" s="11"/>
-      <c r="E88" s="11"/>
+      <c r="A88" s="17"/>
+      <c r="B88" s="17"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="17"/>
+      <c r="E88" s="19"/>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="11"/>
-      <c r="B89" s="11"/>
-      <c r="C89" s="12"/>
-      <c r="D89" s="11"/>
-      <c r="E89" s="11"/>
+      <c r="A89" s="17"/>
+      <c r="B89" s="17"/>
+      <c r="C89" s="18"/>
+      <c r="D89" s="17"/>
+      <c r="E89" s="19"/>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="11"/>
-      <c r="B90" s="11"/>
-      <c r="C90" s="12"/>
-      <c r="D90" s="11"/>
-      <c r="E90" s="11"/>
+      <c r="A90" s="17"/>
+      <c r="B90" s="17"/>
+      <c r="C90" s="18"/>
+      <c r="D90" s="17"/>
+      <c r="E90" s="19"/>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="11"/>
-      <c r="B91" s="11"/>
-      <c r="C91" s="12"/>
-      <c r="D91" s="11"/>
-      <c r="E91" s="11"/>
+      <c r="A91" s="17"/>
+      <c r="B91" s="17"/>
+      <c r="C91" s="18"/>
+      <c r="D91" s="17"/>
+      <c r="E91" s="19"/>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="11"/>
-      <c r="B92" s="11"/>
-      <c r="C92" s="12"/>
-      <c r="D92" s="11"/>
-      <c r="E92" s="11"/>
+      <c r="A92" s="17"/>
+      <c r="B92" s="17"/>
+      <c r="C92" s="18"/>
+      <c r="D92" s="17"/>
+      <c r="E92" s="19"/>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="11"/>
-      <c r="B93" s="11"/>
-      <c r="C93" s="12"/>
-      <c r="D93" s="11"/>
-      <c r="E93" s="11"/>
+      <c r="A93" s="17"/>
+      <c r="B93" s="17"/>
+      <c r="C93" s="18"/>
+      <c r="D93" s="17"/>
+      <c r="E93" s="19"/>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="11"/>
-      <c r="B94" s="11"/>
-      <c r="C94" s="12"/>
-      <c r="D94" s="11"/>
-      <c r="E94" s="11"/>
+      <c r="A94" s="17"/>
+      <c r="B94" s="17"/>
+      <c r="C94" s="18"/>
+      <c r="D94" s="17"/>
+      <c r="E94" s="19"/>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="11"/>
-      <c r="B95" s="11"/>
-      <c r="C95" s="12"/>
-      <c r="D95" s="11"/>
-      <c r="E95" s="11"/>
+      <c r="A95" s="17"/>
+      <c r="B95" s="17"/>
+      <c r="C95" s="18"/>
+      <c r="D95" s="17"/>
+      <c r="E95" s="19"/>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="11"/>
-      <c r="B96" s="11"/>
-      <c r="C96" s="12"/>
-      <c r="D96" s="11"/>
-      <c r="E96" s="11"/>
+      <c r="A96" s="17"/>
+      <c r="B96" s="17"/>
+      <c r="C96" s="18"/>
+      <c r="D96" s="17"/>
+      <c r="E96" s="19"/>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="11"/>
-      <c r="B97" s="11"/>
-      <c r="C97" s="12"/>
-      <c r="D97" s="11"/>
-      <c r="E97" s="11"/>
+      <c r="A97" s="17"/>
+      <c r="B97" s="17"/>
+      <c r="C97" s="18"/>
+      <c r="D97" s="17"/>
+      <c r="E97" s="19"/>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="11"/>
-      <c r="B98" s="11"/>
-      <c r="C98" s="12"/>
-      <c r="D98" s="11"/>
-      <c r="E98" s="11"/>
+      <c r="A98" s="17"/>
+      <c r="B98" s="17"/>
+      <c r="C98" s="18"/>
+      <c r="D98" s="17"/>
+      <c r="E98" s="19"/>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="11"/>
-      <c r="B99" s="11"/>
-      <c r="C99" s="12"/>
-      <c r="D99" s="11"/>
-      <c r="E99" s="11"/>
+      <c r="A99" s="17"/>
+      <c r="B99" s="17"/>
+      <c r="C99" s="18"/>
+      <c r="D99" s="17"/>
+      <c r="E99" s="19"/>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="11"/>
-      <c r="B100" s="11"/>
-      <c r="C100" s="12"/>
-      <c r="D100" s="11"/>
-      <c r="E100" s="11"/>
+      <c r="A100" s="17"/>
+      <c r="B100" s="17"/>
+      <c r="C100" s="18"/>
+      <c r="D100" s="17"/>
+      <c r="E100" s="19"/>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="11"/>
-      <c r="B101" s="11"/>
-      <c r="C101" s="12"/>
-      <c r="D101" s="11"/>
-      <c r="E101" s="11"/>
+      <c r="A101" s="17"/>
+      <c r="B101" s="17"/>
+      <c r="C101" s="18"/>
+      <c r="D101" s="17"/>
+      <c r="E101" s="19"/>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="11"/>
-      <c r="B102" s="11"/>
-      <c r="C102" s="12"/>
-      <c r="D102" s="11"/>
-      <c r="E102" s="11"/>
+      <c r="A102" s="17"/>
+      <c r="B102" s="17"/>
+      <c r="C102" s="18"/>
+      <c r="D102" s="17"/>
+      <c r="E102" s="19"/>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="11"/>
-      <c r="B103" s="11"/>
-      <c r="C103" s="12"/>
-      <c r="D103" s="11"/>
-      <c r="E103" s="11"/>
+      <c r="A103" s="17"/>
+      <c r="B103" s="17"/>
+      <c r="C103" s="18"/>
+      <c r="D103" s="17"/>
+      <c r="E103" s="19"/>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="11"/>
-      <c r="B104" s="11"/>
-      <c r="C104" s="12"/>
-      <c r="D104" s="11"/>
-      <c r="E104" s="11"/>
+      <c r="A104" s="17"/>
+      <c r="B104" s="17"/>
+      <c r="C104" s="18"/>
+      <c r="D104" s="17"/>
+      <c r="E104" s="19"/>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="11"/>
-      <c r="B105" s="11"/>
-      <c r="C105" s="12"/>
-      <c r="D105" s="11"/>
-      <c r="E105" s="11"/>
+      <c r="A105" s="17"/>
+      <c r="B105" s="17"/>
+      <c r="C105" s="18"/>
+      <c r="D105" s="17"/>
+      <c r="E105" s="19"/>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="11"/>
-      <c r="B106" s="11"/>
-      <c r="C106" s="12"/>
-      <c r="D106" s="11"/>
-      <c r="E106" s="11"/>
+      <c r="A106" s="17"/>
+      <c r="B106" s="17"/>
+      <c r="C106" s="18"/>
+      <c r="D106" s="17"/>
+      <c r="E106" s="19"/>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="11"/>
-      <c r="B107" s="11"/>
-      <c r="C107" s="12"/>
-      <c r="D107" s="11"/>
-      <c r="E107" s="11"/>
+      <c r="A107" s="17"/>
+      <c r="B107" s="17"/>
+      <c r="C107" s="18"/>
+      <c r="D107" s="17"/>
+      <c r="E107" s="19"/>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="11"/>
-      <c r="B108" s="11"/>
-      <c r="C108" s="12"/>
-      <c r="D108" s="11"/>
-      <c r="E108" s="11"/>
+      <c r="A108" s="17"/>
+      <c r="B108" s="17"/>
+      <c r="C108" s="18"/>
+      <c r="D108" s="17"/>
+      <c r="E108" s="19"/>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="11"/>
-      <c r="B109" s="11"/>
-      <c r="C109" s="12"/>
-      <c r="D109" s="11"/>
-      <c r="E109" s="11"/>
+      <c r="A109" s="17"/>
+      <c r="B109" s="17"/>
+      <c r="C109" s="18"/>
+      <c r="D109" s="17"/>
+      <c r="E109" s="19"/>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="11"/>
-      <c r="B110" s="11"/>
-      <c r="C110" s="12"/>
-      <c r="D110" s="11"/>
-      <c r="E110" s="11"/>
+      <c r="A110" s="17"/>
+      <c r="B110" s="17"/>
+      <c r="C110" s="18"/>
+      <c r="D110" s="17"/>
+      <c r="E110" s="19"/>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="11"/>
-      <c r="B111" s="11"/>
-      <c r="C111" s="12"/>
-      <c r="D111" s="11"/>
-      <c r="E111" s="11"/>
+      <c r="A111" s="17"/>
+      <c r="B111" s="17"/>
+      <c r="C111" s="18"/>
+      <c r="D111" s="17"/>
+      <c r="E111" s="19"/>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="11"/>
-      <c r="B112" s="11"/>
-      <c r="C112" s="12"/>
-      <c r="D112" s="11"/>
-      <c r="E112" s="11"/>
+      <c r="A112" s="17"/>
+      <c r="B112" s="17"/>
+      <c r="C112" s="18"/>
+      <c r="D112" s="17"/>
+      <c r="E112" s="19"/>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="11"/>
-      <c r="B113" s="11"/>
-      <c r="C113" s="12"/>
-      <c r="D113" s="11"/>
-      <c r="E113" s="11"/>
+      <c r="A113" s="17"/>
+      <c r="B113" s="17"/>
+      <c r="C113" s="18"/>
+      <c r="D113" s="17"/>
+      <c r="E113" s="19"/>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="11"/>
-      <c r="B114" s="11"/>
-      <c r="C114" s="12"/>
-      <c r="D114" s="11"/>
-      <c r="E114" s="11"/>
+      <c r="A114" s="17"/>
+      <c r="B114" s="17"/>
+      <c r="C114" s="18"/>
+      <c r="D114" s="17"/>
+      <c r="E114" s="19"/>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="11"/>
-      <c r="B115" s="11"/>
-      <c r="C115" s="12"/>
-      <c r="D115" s="11"/>
-      <c r="E115" s="11"/>
+      <c r="A115" s="17"/>
+      <c r="B115" s="17"/>
+      <c r="C115" s="18"/>
+      <c r="D115" s="17"/>
+      <c r="E115" s="19"/>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="11"/>
-      <c r="B116" s="11"/>
-      <c r="C116" s="12"/>
-      <c r="D116" s="11"/>
-      <c r="E116" s="11"/>
+      <c r="A116" s="17"/>
+      <c r="B116" s="17"/>
+      <c r="C116" s="18"/>
+      <c r="D116" s="17"/>
+      <c r="E116" s="19"/>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="11"/>
-      <c r="B117" s="11"/>
-      <c r="C117" s="12"/>
-      <c r="D117" s="11"/>
-      <c r="E117" s="11"/>
+      <c r="A117" s="17"/>
+      <c r="B117" s="17"/>
+      <c r="C117" s="18"/>
+      <c r="D117" s="17"/>
+      <c r="E117" s="19"/>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="11"/>
-      <c r="B118" s="11"/>
-      <c r="C118" s="12"/>
-      <c r="D118" s="11"/>
-      <c r="E118" s="11"/>
+      <c r="A118" s="17"/>
+      <c r="B118" s="17"/>
+      <c r="C118" s="18"/>
+      <c r="D118" s="17"/>
+      <c r="E118" s="19"/>
     </row>
     <row r="119" spans="1:5">
-      <c r="A119" s="11"/>
-      <c r="B119" s="11"/>
-      <c r="C119" s="12"/>
-      <c r="D119" s="11"/>
-      <c r="E119" s="11"/>
+      <c r="A119" s="17"/>
+      <c r="B119" s="17"/>
+      <c r="C119" s="18"/>
+      <c r="D119" s="17"/>
+      <c r="E119" s="19"/>
     </row>
     <row r="120" spans="1:5">
-      <c r="A120" s="11"/>
-      <c r="B120" s="11"/>
-      <c r="C120" s="12"/>
-      <c r="D120" s="11"/>
-      <c r="E120" s="11"/>
+      <c r="A120" s="17"/>
+      <c r="B120" s="17"/>
+      <c r="C120" s="18"/>
+      <c r="D120" s="17"/>
+      <c r="E120" s="19"/>
     </row>
     <row r="121" spans="1:5">
-      <c r="A121" s="11"/>
-      <c r="B121" s="11"/>
-      <c r="C121" s="12"/>
-      <c r="D121" s="11"/>
-      <c r="E121" s="11"/>
+      <c r="A121" s="17"/>
+      <c r="B121" s="17"/>
+      <c r="C121" s="18"/>
+      <c r="D121" s="17"/>
+      <c r="E121" s="19"/>
     </row>
     <row r="122" spans="1:5">
-      <c r="A122" s="11"/>
-      <c r="B122" s="11"/>
-      <c r="C122" s="12"/>
-      <c r="D122" s="11"/>
-      <c r="E122" s="11"/>
+      <c r="A122" s="17"/>
+      <c r="B122" s="17"/>
+      <c r="C122" s="18"/>
+      <c r="D122" s="17"/>
+      <c r="E122" s="19"/>
     </row>
     <row r="123" spans="1:5">
-      <c r="A123" s="11"/>
-      <c r="B123" s="11"/>
-      <c r="C123" s="12"/>
-      <c r="D123" s="11"/>
-      <c r="E123" s="11"/>
+      <c r="A123" s="17"/>
+      <c r="B123" s="17"/>
+      <c r="C123" s="18"/>
+      <c r="D123" s="17"/>
+      <c r="E123" s="19"/>
     </row>
     <row r="124" spans="1:5">
-      <c r="A124" s="11"/>
-      <c r="B124" s="11"/>
-      <c r="C124" s="12"/>
-      <c r="D124" s="11"/>
-      <c r="E124" s="11"/>
+      <c r="A124" s="17"/>
+      <c r="B124" s="17"/>
+      <c r="C124" s="18"/>
+      <c r="D124" s="17"/>
+      <c r="E124" s="19"/>
     </row>
     <row r="125" spans="1:5">
-      <c r="A125" s="11"/>
-      <c r="B125" s="11"/>
-      <c r="C125" s="12"/>
-      <c r="D125" s="11"/>
-      <c r="E125" s="11"/>
+      <c r="A125" s="17"/>
+      <c r="B125" s="17"/>
+      <c r="C125" s="18"/>
+      <c r="D125" s="17"/>
+      <c r="E125" s="19"/>
     </row>
     <row r="126" spans="1:5">
-      <c r="A126" s="11"/>
-      <c r="B126" s="11"/>
-      <c r="C126" s="12"/>
-      <c r="D126" s="11"/>
-      <c r="E126" s="11"/>
+      <c r="A126" s="17"/>
+      <c r="B126" s="17"/>
+      <c r="C126" s="18"/>
+      <c r="D126" s="17"/>
+      <c r="E126" s="19"/>
     </row>
     <row r="127" spans="1:5">
-      <c r="A127" s="11"/>
-      <c r="B127" s="11"/>
-      <c r="C127" s="12"/>
-      <c r="D127" s="11"/>
-      <c r="E127" s="11"/>
+      <c r="A127" s="17"/>
+      <c r="B127" s="17"/>
+      <c r="C127" s="18"/>
+      <c r="D127" s="17"/>
+      <c r="E127" s="19"/>
     </row>
     <row r="128" spans="1:5">
-      <c r="A128" s="11"/>
-      <c r="B128" s="11"/>
-      <c r="C128" s="12"/>
-      <c r="D128" s="11"/>
-      <c r="E128" s="11"/>
+      <c r="A128" s="17"/>
+      <c r="B128" s="17"/>
+      <c r="C128" s="18"/>
+      <c r="D128" s="17"/>
+      <c r="E128" s="19"/>
     </row>
     <row r="129" spans="1:5">
-      <c r="A129" s="11"/>
-      <c r="B129" s="11"/>
-      <c r="C129" s="12"/>
-      <c r="D129" s="11"/>
-      <c r="E129" s="11"/>
+      <c r="A129" s="17"/>
+      <c r="B129" s="17"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="17"/>
+      <c r="E129" s="19"/>
     </row>
     <row r="130" spans="1:5">
-      <c r="A130" s="11"/>
-      <c r="B130" s="11"/>
-      <c r="C130" s="12"/>
-      <c r="D130" s="11"/>
-      <c r="E130" s="11"/>
+      <c r="A130" s="17"/>
+      <c r="B130" s="17"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="17"/>
+      <c r="E130" s="19"/>
     </row>
     <row r="131" spans="1:5">
-      <c r="A131" s="11"/>
-      <c r="B131" s="11"/>
-      <c r="C131" s="12"/>
-      <c r="D131" s="11"/>
-      <c r="E131" s="11"/>
+      <c r="A131" s="17"/>
+      <c r="B131" s="17"/>
+      <c r="C131" s="18"/>
+      <c r="D131" s="17"/>
+      <c r="E131" s="19"/>
     </row>
     <row r="132" spans="1:5">
-      <c r="A132" s="11"/>
-      <c r="B132" s="11"/>
-      <c r="C132" s="12"/>
-      <c r="D132" s="11"/>
-      <c r="E132" s="11"/>
+      <c r="A132" s="17"/>
+      <c r="B132" s="17"/>
+      <c r="C132" s="18"/>
+      <c r="D132" s="17"/>
+      <c r="E132" s="19"/>
     </row>
     <row r="133" spans="1:5">
-      <c r="A133" s="11"/>
-      <c r="B133" s="11"/>
-      <c r="C133" s="12"/>
-      <c r="D133" s="11"/>
-      <c r="E133" s="11"/>
+      <c r="A133" s="17"/>
+      <c r="B133" s="17"/>
+      <c r="C133" s="18"/>
+      <c r="D133" s="17"/>
+      <c r="E133" s="19"/>
     </row>
     <row r="134" spans="1:5">
-      <c r="A134" s="11"/>
-      <c r="B134" s="11"/>
-      <c r="C134" s="12"/>
-      <c r="D134" s="11"/>
-      <c r="E134" s="11"/>
+      <c r="A134" s="17"/>
+      <c r="B134" s="17"/>
+      <c r="C134" s="18"/>
+      <c r="D134" s="17"/>
+      <c r="E134" s="19"/>
     </row>
     <row r="135" spans="1:5">
-      <c r="A135" s="11"/>
-      <c r="B135" s="11"/>
-      <c r="C135" s="12"/>
-      <c r="D135" s="11"/>
-      <c r="E135" s="11"/>
+      <c r="A135" s="17"/>
+      <c r="B135" s="17"/>
+      <c r="C135" s="18"/>
+      <c r="D135" s="17"/>
+      <c r="E135" s="19"/>
     </row>
     <row r="136" spans="1:5">
-      <c r="A136" s="11"/>
-      <c r="B136" s="11"/>
-      <c r="C136" s="12"/>
-      <c r="D136" s="11"/>
-      <c r="E136" s="11"/>
+      <c r="A136" s="17"/>
+      <c r="B136" s="17"/>
+      <c r="C136" s="18"/>
+      <c r="D136" s="17"/>
+      <c r="E136" s="19"/>
     </row>
     <row r="137" spans="1:5">
-      <c r="A137" s="11"/>
-      <c r="B137" s="11"/>
-      <c r="C137" s="12"/>
-      <c r="D137" s="11"/>
-      <c r="E137" s="11"/>
+      <c r="A137" s="17"/>
+      <c r="B137" s="17"/>
+      <c r="C137" s="18"/>
+      <c r="D137" s="17"/>
+      <c r="E137" s="19"/>
     </row>
     <row r="138" spans="1:5">
-      <c r="A138" s="11"/>
-      <c r="B138" s="11"/>
-      <c r="C138" s="12"/>
-      <c r="D138" s="11"/>
-      <c r="E138" s="11"/>
+      <c r="A138" s="17"/>
+      <c r="B138" s="17"/>
+      <c r="C138" s="18"/>
+      <c r="D138" s="17"/>
+      <c r="E138" s="19"/>
     </row>
     <row r="139" spans="1:5">
-      <c r="A139" s="11"/>
-      <c r="B139" s="11"/>
-      <c r="C139" s="12"/>
-      <c r="D139" s="11"/>
-      <c r="E139" s="11"/>
+      <c r="A139" s="17"/>
+      <c r="B139" s="17"/>
+      <c r="C139" s="18"/>
+      <c r="D139" s="17"/>
+      <c r="E139" s="19"/>
     </row>
     <row r="140" spans="1:5">
-      <c r="A140" s="11"/>
-      <c r="B140" s="11"/>
-      <c r="C140" s="12"/>
-      <c r="D140" s="11"/>
-      <c r="E140" s="11"/>
+      <c r="A140" s="17"/>
+      <c r="B140" s="17"/>
+      <c r="C140" s="18"/>
+      <c r="D140" s="17"/>
+      <c r="E140" s="19"/>
     </row>
     <row r="141" spans="1:5">
-      <c r="A141" s="11"/>
-      <c r="B141" s="11"/>
-      <c r="C141" s="12"/>
-      <c r="D141" s="11"/>
-      <c r="E141" s="11"/>
+      <c r="A141" s="17"/>
+      <c r="B141" s="17"/>
+      <c r="C141" s="18"/>
+      <c r="D141" s="17"/>
+      <c r="E141" s="19"/>
     </row>
     <row r="142" spans="1:5">
-      <c r="A142" s="11"/>
-      <c r="B142" s="11"/>
-      <c r="C142" s="12"/>
-      <c r="D142" s="11"/>
-      <c r="E142" s="11"/>
+      <c r="A142" s="17"/>
+      <c r="B142" s="17"/>
+      <c r="C142" s="18"/>
+      <c r="D142" s="17"/>
+      <c r="E142" s="19"/>
     </row>
     <row r="143" spans="1:5">
-      <c r="A143" s="11"/>
-      <c r="B143" s="11"/>
-      <c r="C143" s="12"/>
-      <c r="D143" s="11"/>
-      <c r="E143" s="11"/>
+      <c r="A143" s="17"/>
+      <c r="B143" s="17"/>
+      <c r="C143" s="18"/>
+      <c r="D143" s="17"/>
+      <c r="E143" s="19"/>
     </row>
     <row r="144" spans="1:5">
-      <c r="A144" s="11"/>
-      <c r="B144" s="11"/>
-      <c r="C144" s="12"/>
-      <c r="D144" s="11"/>
-      <c r="E144" s="11"/>
+      <c r="A144" s="17"/>
+      <c r="B144" s="17"/>
+      <c r="C144" s="18"/>
+      <c r="D144" s="17"/>
+      <c r="E144" s="19"/>
     </row>
     <row r="145" spans="1:5">
-      <c r="A145" s="11"/>
-      <c r="B145" s="11"/>
-      <c r="C145" s="12"/>
-      <c r="D145" s="11"/>
-      <c r="E145" s="11"/>
+      <c r="A145" s="17"/>
+      <c r="B145" s="17"/>
+      <c r="C145" s="18"/>
+      <c r="D145" s="17"/>
+      <c r="E145" s="19"/>
     </row>
     <row r="146" spans="1:5">
-      <c r="A146" s="11"/>
-      <c r="B146" s="11"/>
-      <c r="C146" s="12"/>
-      <c r="D146" s="11"/>
-      <c r="E146" s="11"/>
+      <c r="A146" s="17"/>
+      <c r="B146" s="17"/>
+      <c r="C146" s="18"/>
+      <c r="D146" s="17"/>
+      <c r="E146" s="19"/>
     </row>
     <row r="147" spans="1:5">
-      <c r="A147" s="11"/>
-      <c r="B147" s="11"/>
-      <c r="C147" s="12"/>
-      <c r="D147" s="11"/>
-      <c r="E147" s="11"/>
+      <c r="A147" s="17"/>
+      <c r="B147" s="17"/>
+      <c r="C147" s="18"/>
+      <c r="D147" s="17"/>
+      <c r="E147" s="19"/>
     </row>
     <row r="148" spans="1:5">
-      <c r="A148" s="11"/>
-      <c r="B148" s="11"/>
-      <c r="C148" s="12"/>
-      <c r="D148" s="11"/>
-      <c r="E148" s="11"/>
+      <c r="A148" s="17"/>
+      <c r="B148" s="17"/>
+      <c r="C148" s="18"/>
+      <c r="D148" s="17"/>
+      <c r="E148" s="19"/>
     </row>
     <row r="149" spans="1:5">
-      <c r="A149" s="11"/>
-      <c r="B149" s="11"/>
-      <c r="C149" s="12"/>
-      <c r="D149" s="11"/>
-      <c r="E149" s="11"/>
+      <c r="A149" s="17"/>
+      <c r="B149" s="17"/>
+      <c r="C149" s="18"/>
+      <c r="D149" s="17"/>
+      <c r="E149" s="19"/>
     </row>
     <row r="150" spans="1:5">
-      <c r="A150" s="11"/>
-      <c r="B150" s="11"/>
-      <c r="C150" s="12"/>
-      <c r="D150" s="11"/>
-      <c r="E150" s="11"/>
+      <c r="A150" s="17"/>
+      <c r="B150" s="17"/>
+      <c r="C150" s="18"/>
+      <c r="D150" s="17"/>
+      <c r="E150" s="19"/>
     </row>
     <row r="151" spans="1:5">
-      <c r="A151" s="11"/>
-      <c r="B151" s="11"/>
-      <c r="C151" s="12"/>
-      <c r="D151" s="11"/>
-      <c r="E151" s="11"/>
+      <c r="A151" s="17"/>
+      <c r="B151" s="17"/>
+      <c r="C151" s="18"/>
+      <c r="D151" s="17"/>
+      <c r="E151" s="19"/>
     </row>
     <row r="152" spans="1:5">
-      <c r="A152" s="11"/>
-      <c r="B152" s="11"/>
-      <c r="C152" s="12"/>
-      <c r="D152" s="11"/>
-      <c r="E152" s="11"/>
+      <c r="A152" s="17"/>
+      <c r="B152" s="17"/>
+      <c r="C152" s="18"/>
+      <c r="D152" s="17"/>
+      <c r="E152" s="19"/>
     </row>
     <row r="153" spans="1:5">
-      <c r="A153" s="11"/>
-      <c r="B153" s="11"/>
-      <c r="C153" s="12"/>
-      <c r="D153" s="11"/>
-      <c r="E153" s="11"/>
+      <c r="A153" s="17"/>
+      <c r="B153" s="17"/>
+      <c r="C153" s="18"/>
+      <c r="D153" s="17"/>
+      <c r="E153" s="19"/>
     </row>
     <row r="154" spans="1:5">
-      <c r="A154" s="11"/>
-      <c r="B154" s="11"/>
-      <c r="C154" s="12"/>
-      <c r="D154" s="11"/>
-      <c r="E154" s="11"/>
+      <c r="A154" s="17"/>
+      <c r="B154" s="17"/>
+      <c r="C154" s="18"/>
+      <c r="D154" s="17"/>
+      <c r="E154" s="19"/>
     </row>
     <row r="155" spans="1:5">
-      <c r="A155" s="11"/>
-      <c r="B155" s="11"/>
-      <c r="C155" s="12"/>
-      <c r="D155" s="11"/>
-      <c r="E155" s="11"/>
+      <c r="A155" s="17"/>
+      <c r="B155" s="17"/>
+      <c r="C155" s="18"/>
+      <c r="D155" s="17"/>
+      <c r="E155" s="19"/>
     </row>
     <row r="156" spans="1:5">
-      <c r="A156" s="11"/>
-      <c r="B156" s="11"/>
-      <c r="C156" s="12"/>
-      <c r="D156" s="11"/>
-      <c r="E156" s="11"/>
+      <c r="A156" s="17"/>
+      <c r="B156" s="17"/>
+      <c r="C156" s="18"/>
+      <c r="D156" s="17"/>
+      <c r="E156" s="19"/>
     </row>
     <row r="157" spans="1:5">
-      <c r="A157" s="11"/>
-      <c r="B157" s="11"/>
-      <c r="C157" s="12"/>
-      <c r="D157" s="11"/>
-      <c r="E157" s="11"/>
+      <c r="A157" s="17"/>
+      <c r="B157" s="17"/>
+      <c r="C157" s="18"/>
+      <c r="D157" s="17"/>
+      <c r="E157" s="19"/>
     </row>
     <row r="158" spans="1:5">
-      <c r="A158" s="11"/>
-      <c r="B158" s="11"/>
-      <c r="C158" s="12"/>
-      <c r="D158" s="11"/>
-      <c r="E158" s="11"/>
+      <c r="A158" s="17"/>
+      <c r="B158" s="17"/>
+      <c r="C158" s="18"/>
+      <c r="D158" s="17"/>
+      <c r="E158" s="19"/>
     </row>
     <row r="159" spans="1:5">
-      <c r="A159" s="11"/>
-      <c r="B159" s="11"/>
-      <c r="C159" s="12"/>
-      <c r="D159" s="11"/>
-      <c r="E159" s="11"/>
+      <c r="A159" s="17"/>
+      <c r="B159" s="17"/>
+      <c r="C159" s="18"/>
+      <c r="D159" s="17"/>
+      <c r="E159" s="19"/>
     </row>
     <row r="160" spans="1:5">
-      <c r="A160" s="11"/>
-      <c r="B160" s="11"/>
-      <c r="C160" s="12"/>
-      <c r="D160" s="11"/>
-      <c r="E160" s="11"/>
+      <c r="A160" s="17"/>
+      <c r="B160" s="17"/>
+      <c r="C160" s="18"/>
+      <c r="D160" s="17"/>
+      <c r="E160" s="19"/>
     </row>
     <row r="161" spans="1:5">
-      <c r="A161" s="11"/>
-      <c r="B161" s="11"/>
-      <c r="C161" s="12"/>
-      <c r="D161" s="11"/>
-      <c r="E161" s="11"/>
+      <c r="A161" s="17"/>
+      <c r="B161" s="17"/>
+      <c r="C161" s="18"/>
+      <c r="D161" s="17"/>
+      <c r="E161" s="19"/>
     </row>
     <row r="162" spans="1:5">
-      <c r="A162" s="11"/>
-      <c r="B162" s="11"/>
-      <c r="C162" s="12"/>
-      <c r="D162" s="11"/>
-      <c r="E162" s="11"/>
+      <c r="A162" s="17"/>
+      <c r="B162" s="17"/>
+      <c r="C162" s="18"/>
+      <c r="D162" s="17"/>
+      <c r="E162" s="19"/>
     </row>
     <row r="163" spans="1:5">
-      <c r="A163" s="11"/>
-      <c r="B163" s="11"/>
-      <c r="C163" s="12"/>
-      <c r="D163" s="11"/>
-      <c r="E163" s="11"/>
+      <c r="A163" s="17"/>
+      <c r="B163" s="17"/>
+      <c r="C163" s="18"/>
+      <c r="D163" s="17"/>
+      <c r="E163" s="19"/>
     </row>
     <row r="164" spans="1:5">
-      <c r="A164" s="11"/>
-      <c r="B164" s="11"/>
-      <c r="C164" s="12"/>
-      <c r="D164" s="11"/>
-      <c r="E164" s="11"/>
+      <c r="A164" s="17"/>
+      <c r="B164" s="17"/>
+      <c r="C164" s="18"/>
+      <c r="D164" s="17"/>
+      <c r="E164" s="19"/>
     </row>
     <row r="165" spans="1:5">
-      <c r="A165" s="11"/>
-      <c r="B165" s="11"/>
-      <c r="C165" s="12"/>
-      <c r="D165" s="11"/>
-      <c r="E165" s="11"/>
+      <c r="A165" s="17"/>
+      <c r="B165" s="17"/>
+      <c r="C165" s="18"/>
+      <c r="D165" s="17"/>
+      <c r="E165" s="19"/>
     </row>
     <row r="166" spans="1:5">
-      <c r="A166" s="11"/>
-      <c r="B166" s="11"/>
-      <c r="C166" s="12"/>
-      <c r="D166" s="11"/>
-      <c r="E166" s="11"/>
+      <c r="A166" s="17"/>
+      <c r="B166" s="17"/>
+      <c r="C166" s="18"/>
+      <c r="D166" s="17"/>
+      <c r="E166" s="19"/>
     </row>
     <row r="167" spans="1:5">
-      <c r="A167" s="11"/>
-      <c r="B167" s="11"/>
-      <c r="C167" s="12"/>
-      <c r="D167" s="11"/>
-      <c r="E167" s="11"/>
+      <c r="A167" s="17"/>
+      <c r="B167" s="17"/>
+      <c r="C167" s="18"/>
+      <c r="D167" s="17"/>
+      <c r="E167" s="19"/>
     </row>
     <row r="168" spans="1:5">
-      <c r="A168" s="11"/>
-      <c r="B168" s="11"/>
-      <c r="C168" s="12"/>
-      <c r="D168" s="11"/>
-      <c r="E168" s="11"/>
+      <c r="A168" s="17"/>
+      <c r="B168" s="17"/>
+      <c r="C168" s="18"/>
+      <c r="D168" s="17"/>
+      <c r="E168" s="19"/>
     </row>
     <row r="169" spans="1:5">
-      <c r="A169" s="11"/>
-      <c r="B169" s="11"/>
-      <c r="C169" s="12"/>
-      <c r="D169" s="11"/>
-      <c r="E169" s="11"/>
+      <c r="A169" s="17"/>
+      <c r="B169" s="17"/>
+      <c r="C169" s="18"/>
+      <c r="D169" s="17"/>
+      <c r="E169" s="19"/>
     </row>
     <row r="170" spans="1:5">
-      <c r="A170" s="11"/>
-      <c r="B170" s="11"/>
-      <c r="C170" s="12"/>
-      <c r="D170" s="11"/>
-      <c r="E170" s="11"/>
+      <c r="A170" s="17"/>
+      <c r="B170" s="17"/>
+      <c r="C170" s="18"/>
+      <c r="D170" s="17"/>
+      <c r="E170" s="19"/>
     </row>
     <row r="171" spans="1:5">
-      <c r="A171" s="11"/>
-      <c r="B171" s="11"/>
-      <c r="C171" s="12"/>
-      <c r="D171" s="11"/>
-      <c r="E171" s="11"/>
+      <c r="A171" s="17"/>
+      <c r="B171" s="17"/>
+      <c r="C171" s="18"/>
+      <c r="D171" s="17"/>
+      <c r="E171" s="19"/>
     </row>
     <row r="172" spans="1:5">
-      <c r="A172" s="11"/>
-      <c r="B172" s="11"/>
-      <c r="C172" s="12"/>
-      <c r="D172" s="11"/>
-      <c r="E172" s="11"/>
+      <c r="A172" s="17"/>
+      <c r="B172" s="17"/>
+      <c r="C172" s="18"/>
+      <c r="D172" s="17"/>
+      <c r="E172" s="19"/>
     </row>
     <row r="173" spans="1:5">
-      <c r="A173" s="11"/>
-      <c r="B173" s="11"/>
-      <c r="C173" s="12"/>
-      <c r="D173" s="11"/>
-      <c r="E173" s="11"/>
+      <c r="A173" s="17"/>
+      <c r="B173" s="17"/>
+      <c r="C173" s="18"/>
+      <c r="D173" s="17"/>
+      <c r="E173" s="19"/>
     </row>
     <row r="174" spans="1:5">
-      <c r="A174" s="11"/>
-      <c r="B174" s="11"/>
-      <c r="C174" s="12"/>
-      <c r="D174" s="11"/>
-      <c r="E174" s="11"/>
+      <c r="A174" s="17"/>
+      <c r="B174" s="17"/>
+      <c r="C174" s="18"/>
+      <c r="D174" s="17"/>
+      <c r="E174" s="19"/>
     </row>
     <row r="175" spans="1:5">
-      <c r="A175" s="11"/>
-      <c r="B175" s="11"/>
-      <c r="C175" s="12"/>
-      <c r="D175" s="11"/>
-      <c r="E175" s="11"/>
+      <c r="A175" s="17"/>
+      <c r="B175" s="17"/>
+      <c r="C175" s="18"/>
+      <c r="D175" s="17"/>
+      <c r="E175" s="19"/>
     </row>
     <row r="176" spans="1:5">
-      <c r="A176" s="11"/>
-      <c r="B176" s="11"/>
-      <c r="C176" s="12"/>
-      <c r="D176" s="11"/>
-      <c r="E176" s="11"/>
+      <c r="A176" s="17"/>
+      <c r="B176" s="17"/>
+      <c r="C176" s="18"/>
+      <c r="D176" s="17"/>
+      <c r="E176" s="19"/>
     </row>
     <row r="177" spans="1:5">
-      <c r="A177" s="11"/>
-      <c r="B177" s="11"/>
-      <c r="C177" s="12"/>
-      <c r="D177" s="11"/>
-      <c r="E177" s="11"/>
-    </row>
-    <row r="178" ht="15" spans="1:5">
-      <c r="A178" s="11"/>
-      <c r="B178" s="11"/>
-      <c r="C178" s="12"/>
-      <c r="D178" s="11"/>
-      <c r="E178" s="11"/>
-    </row>
-    <row r="179" ht="15" spans="1:5">
-      <c r="A179" s="15"/>
-      <c r="B179" s="15"/>
-      <c r="C179" s="15"/>
-      <c r="D179" s="15"/>
-      <c r="E179" s="15"/>
-    </row>
-    <row r="180" ht="15" spans="1:5">
-      <c r="A180" s="15"/>
-      <c r="B180" s="15"/>
-      <c r="C180" s="15"/>
-      <c r="D180" s="15"/>
-      <c r="E180" s="15"/>
-    </row>
-    <row r="181" ht="15" spans="1:5">
-      <c r="A181" s="15"/>
-      <c r="B181" s="15"/>
-      <c r="C181" s="15"/>
-      <c r="D181" s="15"/>
-      <c r="E181" s="15"/>
+      <c r="A177" s="17"/>
+      <c r="B177" s="17"/>
+      <c r="C177" s="18"/>
+      <c r="D177" s="17"/>
+      <c r="E177" s="19"/>
+    </row>
+    <row r="178" ht="14.75" spans="1:5">
+      <c r="A178" s="17"/>
+      <c r="B178" s="17"/>
+      <c r="C178" s="18"/>
+      <c r="D178" s="17"/>
+      <c r="E178" s="19"/>
+    </row>
+    <row r="179" ht="14.75" spans="1:5">
+      <c r="A179" s="22"/>
+      <c r="B179" s="22"/>
+      <c r="C179" s="22"/>
+      <c r="D179" s="22"/>
+      <c r="E179" s="23"/>
+    </row>
+    <row r="180" ht="14.75" spans="1:5">
+      <c r="A180" s="22"/>
+      <c r="B180" s="22"/>
+      <c r="C180" s="22"/>
+      <c r="D180" s="22"/>
+      <c r="E180" s="23"/>
+    </row>
+    <row r="181" ht="14.75" spans="1:5">
+      <c r="A181" s="22"/>
+      <c r="B181" s="22"/>
+      <c r="C181" s="22"/>
+      <c r="D181" s="22"/>
+      <c r="E181" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tools/Luban/DataTables/Datas/R_任务.xlsx
+++ b/Tools/Luban/DataTables/Datas/R_任务.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1197,9 +1197,6 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1213,6 +1210,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1541,7 +1541,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K181"/>
-  <sheetFormatPr defaultColWidth="12" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="12" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="12" style="1"/>
     <col min="3" max="3" width="16" style="1" customWidth="1"/>
@@ -1695,7 +1695,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="2:10">
       <c r="B5" s="11">
         <v>1001</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="2:11">
       <c r="B6" s="11">
         <v>1002</v>
       </c>
@@ -1746,14 +1746,14 @@
         <v>42</v>
       </c>
       <c r="J6" s="11">
-        <v>1003</v>
-      </c>
-      <c r="K6" s="16" t="s">
+        <v>1004</v>
+      </c>
+      <c r="K6" s="21" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="17"/>
+      <c r="A7" s="16"/>
       <c r="B7" s="11">
         <v>1003</v>
       </c>
@@ -1781,12 +1781,12 @@
       <c r="J7" s="11">
         <v>1004</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="21" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="17"/>
+      <c r="A8" s="16"/>
       <c r="B8" s="11">
         <v>1004</v>
       </c>
@@ -1819,7 +1819,7 @@
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="17"/>
+      <c r="A9" s="16"/>
       <c r="B9" s="11">
         <v>1005</v>
       </c>
@@ -1845,10 +1845,10 @@
       <c r="J9" s="11">
         <v>1006</v>
       </c>
-      <c r="K9" s="16"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="17"/>
+      <c r="K9" s="21"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="16"/>
       <c r="B10" s="11">
         <v>1006</v>
       </c>
@@ -1876,7 +1876,7 @@
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="17"/>
+      <c r="A11" s="16"/>
       <c r="B11" s="11">
         <v>1007</v>
       </c>
@@ -1907,7 +1907,7 @@
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="17"/>
+      <c r="A12" s="16"/>
       <c r="B12" s="11">
         <v>1008</v>
       </c>
@@ -1940,7 +1940,7 @@
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="17"/>
+      <c r="A13" s="16"/>
       <c r="B13" s="11">
         <v>1009</v>
       </c>
@@ -1973,7 +1973,7 @@
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="17"/>
+      <c r="A14" s="16"/>
       <c r="B14" s="11">
         <v>1010</v>
       </c>
@@ -2004,17 +2004,17 @@
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16">
         <v>1011</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="16">
         <v>2</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="18" t="s">
         <v>90</v>
       </c>
       <c r="F15" s="2" t="s">
@@ -2034,7 +2034,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="2:11">
       <c r="B16" s="1">
         <v>1012</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="2:11">
       <c r="B17" s="1">
         <v>1013</v>
       </c>
@@ -2099,7 +2099,7 @@
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="17"/>
+      <c r="A18" s="16"/>
       <c r="B18" s="1">
         <v>1014</v>
       </c>
@@ -2115,13 +2115,13 @@
       <c r="F18" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G18" s="20" t="s">
+      <c r="G18" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="19">
         <v>292</v>
       </c>
-      <c r="I18" s="20">
+      <c r="I18" s="19">
         <v>293</v>
       </c>
       <c r="J18" s="1">
@@ -2132,7 +2132,7 @@
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="17"/>
+      <c r="A19" s="16"/>
       <c r="B19" s="1">
         <v>1015</v>
       </c>
@@ -2148,11 +2148,11 @@
       <c r="F19" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G19" s="20" t="s">
+      <c r="G19" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20" t="s">
+      <c r="H19" s="19"/>
+      <c r="I19" s="19" t="s">
         <v>112</v>
       </c>
       <c r="J19" s="1">
@@ -2163,7 +2163,7 @@
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="17"/>
+      <c r="A20" s="16"/>
       <c r="B20" s="1">
         <v>1016</v>
       </c>
@@ -2176,1121 +2176,1121 @@
       <c r="E20" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G20" s="20" t="s">
+      <c r="G20" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="H20" s="20" t="s">
+      <c r="H20" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="I20" s="20" t="s">
+      <c r="I20" s="19" t="s">
         <v>118</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="17"/>
-      <c r="E21" s="21"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="17"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="17"/>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="17"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="17"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="19"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="19"/>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="19"/>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="19"/>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="19"/>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="19"/>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="19"/>
+    <row r="21" spans="1:5">
+      <c r="A21" s="16"/>
+      <c r="E21" s="20"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="16"/>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="16"/>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="16"/>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="16"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="18"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="18"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="18"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="18"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="18"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="18"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="18"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="19"/>
+      <c r="A33" s="16"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="18"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="19"/>
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="18"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="19"/>
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="18"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="19"/>
+      <c r="A36" s="16"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="18"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="19"/>
+      <c r="A37" s="16"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="18"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="19"/>
+      <c r="A38" s="16"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="18"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="19"/>
+      <c r="A39" s="16"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="18"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="19"/>
+      <c r="A40" s="16"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="18"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="19"/>
+      <c r="A41" s="16"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="18"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="19"/>
+      <c r="A42" s="16"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="18"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="19"/>
+      <c r="A43" s="16"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="18"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="19"/>
+      <c r="A44" s="16"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="18"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="19"/>
+      <c r="A45" s="16"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="18"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="19"/>
+      <c r="A46" s="16"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="18"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="19"/>
+      <c r="A47" s="16"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="18"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="19"/>
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="18"/>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="19"/>
+      <c r="A49" s="16"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="18"/>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="19"/>
+      <c r="A50" s="16"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="18"/>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="17"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="19"/>
+      <c r="A51" s="16"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="18"/>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="19"/>
+      <c r="A52" s="16"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="18"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="19"/>
+      <c r="A53" s="16"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="18"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="19"/>
+      <c r="A54" s="16"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="18"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="19"/>
+      <c r="A55" s="16"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="18"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="19"/>
+      <c r="A56" s="16"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="18"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="17"/>
-      <c r="B57" s="17"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="19"/>
+      <c r="A57" s="16"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="18"/>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="17"/>
-      <c r="B58" s="17"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="19"/>
+      <c r="A58" s="16"/>
+      <c r="B58" s="16"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="18"/>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="17"/>
-      <c r="B59" s="17"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="19"/>
+      <c r="A59" s="16"/>
+      <c r="B59" s="16"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="18"/>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="17"/>
-      <c r="B60" s="17"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="19"/>
+      <c r="A60" s="16"/>
+      <c r="B60" s="16"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="18"/>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="17"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="17"/>
-      <c r="E61" s="19"/>
+      <c r="A61" s="16"/>
+      <c r="B61" s="16"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="18"/>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="17"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="17"/>
-      <c r="E62" s="19"/>
+      <c r="A62" s="16"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="18"/>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="17"/>
-      <c r="B63" s="17"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="17"/>
-      <c r="E63" s="19"/>
+      <c r="A63" s="16"/>
+      <c r="B63" s="16"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="18"/>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="17"/>
-      <c r="B64" s="17"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="17"/>
-      <c r="E64" s="19"/>
+      <c r="A64" s="16"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="18"/>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="17"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="17"/>
-      <c r="E65" s="19"/>
+      <c r="A65" s="16"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="18"/>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="17"/>
-      <c r="B66" s="17"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="19"/>
+      <c r="A66" s="16"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="18"/>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="17"/>
-      <c r="B67" s="17"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="19"/>
+      <c r="A67" s="16"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="18"/>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="17"/>
-      <c r="B68" s="17"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="17"/>
-      <c r="E68" s="19"/>
+      <c r="A68" s="16"/>
+      <c r="B68" s="16"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="18"/>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="17"/>
-      <c r="B69" s="17"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="17"/>
-      <c r="E69" s="19"/>
+      <c r="A69" s="16"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="18"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="17"/>
-      <c r="B70" s="17"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="17"/>
-      <c r="E70" s="19"/>
+      <c r="A70" s="16"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="17"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="18"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="17"/>
-      <c r="B71" s="17"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="17"/>
-      <c r="E71" s="19"/>
+      <c r="A71" s="16"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="17"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="18"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="17"/>
-      <c r="B72" s="17"/>
-      <c r="C72" s="18"/>
-      <c r="D72" s="17"/>
-      <c r="E72" s="19"/>
+      <c r="A72" s="16"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="18"/>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="17"/>
-      <c r="B73" s="17"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="17"/>
-      <c r="E73" s="19"/>
+      <c r="A73" s="16"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="17"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="18"/>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="17"/>
-      <c r="B74" s="17"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="17"/>
-      <c r="E74" s="19"/>
+      <c r="A74" s="16"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="18"/>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="17"/>
-      <c r="B75" s="17"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="17"/>
-      <c r="E75" s="19"/>
+      <c r="A75" s="16"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="17"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="18"/>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="17"/>
-      <c r="B76" s="17"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="17"/>
-      <c r="E76" s="19"/>
+      <c r="A76" s="16"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="17"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="18"/>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="17"/>
-      <c r="B77" s="17"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="19"/>
+      <c r="A77" s="16"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="17"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="18"/>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="17"/>
-      <c r="B78" s="17"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="17"/>
-      <c r="E78" s="19"/>
+      <c r="A78" s="16"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="17"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="18"/>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="17"/>
-      <c r="B79" s="17"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="17"/>
-      <c r="E79" s="19"/>
+      <c r="A79" s="16"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="17"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="18"/>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="17"/>
-      <c r="B80" s="17"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="19"/>
+      <c r="A80" s="16"/>
+      <c r="B80" s="16"/>
+      <c r="C80" s="17"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="18"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="17"/>
-      <c r="B81" s="17"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="19"/>
+      <c r="A81" s="16"/>
+      <c r="B81" s="16"/>
+      <c r="C81" s="17"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="18"/>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="17"/>
-      <c r="B82" s="17"/>
-      <c r="C82" s="18"/>
-      <c r="D82" s="17"/>
-      <c r="E82" s="19"/>
+      <c r="A82" s="16"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="17"/>
+      <c r="D82" s="16"/>
+      <c r="E82" s="18"/>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="17"/>
-      <c r="B83" s="17"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="17"/>
-      <c r="E83" s="19"/>
+      <c r="A83" s="16"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="18"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="17"/>
-      <c r="B84" s="17"/>
-      <c r="C84" s="18"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="19"/>
+      <c r="A84" s="16"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="18"/>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="17"/>
-      <c r="B85" s="17"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="17"/>
-      <c r="E85" s="19"/>
+      <c r="A85" s="16"/>
+      <c r="B85" s="16"/>
+      <c r="C85" s="17"/>
+      <c r="D85" s="16"/>
+      <c r="E85" s="18"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="17"/>
-      <c r="B86" s="17"/>
-      <c r="C86" s="18"/>
-      <c r="D86" s="17"/>
-      <c r="E86" s="19"/>
+      <c r="A86" s="16"/>
+      <c r="B86" s="16"/>
+      <c r="C86" s="17"/>
+      <c r="D86" s="16"/>
+      <c r="E86" s="18"/>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="17"/>
-      <c r="B87" s="17"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="17"/>
-      <c r="E87" s="19"/>
+      <c r="A87" s="16"/>
+      <c r="B87" s="16"/>
+      <c r="C87" s="17"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="18"/>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="17"/>
-      <c r="B88" s="17"/>
-      <c r="C88" s="18"/>
-      <c r="D88" s="17"/>
-      <c r="E88" s="19"/>
+      <c r="A88" s="16"/>
+      <c r="B88" s="16"/>
+      <c r="C88" s="17"/>
+      <c r="D88" s="16"/>
+      <c r="E88" s="18"/>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="17"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="18"/>
-      <c r="D89" s="17"/>
-      <c r="E89" s="19"/>
+      <c r="A89" s="16"/>
+      <c r="B89" s="16"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="18"/>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="17"/>
-      <c r="B90" s="17"/>
-      <c r="C90" s="18"/>
-      <c r="D90" s="17"/>
-      <c r="E90" s="19"/>
+      <c r="A90" s="16"/>
+      <c r="B90" s="16"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="18"/>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="17"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="18"/>
-      <c r="D91" s="17"/>
-      <c r="E91" s="19"/>
+      <c r="A91" s="16"/>
+      <c r="B91" s="16"/>
+      <c r="C91" s="17"/>
+      <c r="D91" s="16"/>
+      <c r="E91" s="18"/>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="17"/>
-      <c r="B92" s="17"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="17"/>
-      <c r="E92" s="19"/>
+      <c r="A92" s="16"/>
+      <c r="B92" s="16"/>
+      <c r="C92" s="17"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="18"/>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="17"/>
-      <c r="B93" s="17"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="17"/>
-      <c r="E93" s="19"/>
+      <c r="A93" s="16"/>
+      <c r="B93" s="16"/>
+      <c r="C93" s="17"/>
+      <c r="D93" s="16"/>
+      <c r="E93" s="18"/>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="17"/>
-      <c r="B94" s="17"/>
-      <c r="C94" s="18"/>
-      <c r="D94" s="17"/>
-      <c r="E94" s="19"/>
+      <c r="A94" s="16"/>
+      <c r="B94" s="16"/>
+      <c r="C94" s="17"/>
+      <c r="D94" s="16"/>
+      <c r="E94" s="18"/>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="17"/>
-      <c r="B95" s="17"/>
-      <c r="C95" s="18"/>
-      <c r="D95" s="17"/>
-      <c r="E95" s="19"/>
+      <c r="A95" s="16"/>
+      <c r="B95" s="16"/>
+      <c r="C95" s="17"/>
+      <c r="D95" s="16"/>
+      <c r="E95" s="18"/>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="17"/>
-      <c r="B96" s="17"/>
-      <c r="C96" s="18"/>
-      <c r="D96" s="17"/>
-      <c r="E96" s="19"/>
+      <c r="A96" s="16"/>
+      <c r="B96" s="16"/>
+      <c r="C96" s="17"/>
+      <c r="D96" s="16"/>
+      <c r="E96" s="18"/>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="17"/>
-      <c r="B97" s="17"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="17"/>
-      <c r="E97" s="19"/>
+      <c r="A97" s="16"/>
+      <c r="B97" s="16"/>
+      <c r="C97" s="17"/>
+      <c r="D97" s="16"/>
+      <c r="E97" s="18"/>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="17"/>
-      <c r="B98" s="17"/>
-      <c r="C98" s="18"/>
-      <c r="D98" s="17"/>
-      <c r="E98" s="19"/>
+      <c r="A98" s="16"/>
+      <c r="B98" s="16"/>
+      <c r="C98" s="17"/>
+      <c r="D98" s="16"/>
+      <c r="E98" s="18"/>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="17"/>
-      <c r="B99" s="17"/>
-      <c r="C99" s="18"/>
-      <c r="D99" s="17"/>
-      <c r="E99" s="19"/>
+      <c r="A99" s="16"/>
+      <c r="B99" s="16"/>
+      <c r="C99" s="17"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="18"/>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="17"/>
-      <c r="B100" s="17"/>
-      <c r="C100" s="18"/>
-      <c r="D100" s="17"/>
-      <c r="E100" s="19"/>
+      <c r="A100" s="16"/>
+      <c r="B100" s="16"/>
+      <c r="C100" s="17"/>
+      <c r="D100" s="16"/>
+      <c r="E100" s="18"/>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="17"/>
-      <c r="B101" s="17"/>
-      <c r="C101" s="18"/>
-      <c r="D101" s="17"/>
-      <c r="E101" s="19"/>
+      <c r="A101" s="16"/>
+      <c r="B101" s="16"/>
+      <c r="C101" s="17"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="18"/>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="17"/>
-      <c r="B102" s="17"/>
-      <c r="C102" s="18"/>
-      <c r="D102" s="17"/>
-      <c r="E102" s="19"/>
+      <c r="A102" s="16"/>
+      <c r="B102" s="16"/>
+      <c r="C102" s="17"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="18"/>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="17"/>
-      <c r="B103" s="17"/>
-      <c r="C103" s="18"/>
-      <c r="D103" s="17"/>
-      <c r="E103" s="19"/>
+      <c r="A103" s="16"/>
+      <c r="B103" s="16"/>
+      <c r="C103" s="17"/>
+      <c r="D103" s="16"/>
+      <c r="E103" s="18"/>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="17"/>
-      <c r="B104" s="17"/>
-      <c r="C104" s="18"/>
-      <c r="D104" s="17"/>
-      <c r="E104" s="19"/>
+      <c r="A104" s="16"/>
+      <c r="B104" s="16"/>
+      <c r="C104" s="17"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="18"/>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="17"/>
-      <c r="B105" s="17"/>
-      <c r="C105" s="18"/>
-      <c r="D105" s="17"/>
-      <c r="E105" s="19"/>
+      <c r="A105" s="16"/>
+      <c r="B105" s="16"/>
+      <c r="C105" s="17"/>
+      <c r="D105" s="16"/>
+      <c r="E105" s="18"/>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="17"/>
-      <c r="B106" s="17"/>
-      <c r="C106" s="18"/>
-      <c r="D106" s="17"/>
-      <c r="E106" s="19"/>
+      <c r="A106" s="16"/>
+      <c r="B106" s="16"/>
+      <c r="C106" s="17"/>
+      <c r="D106" s="16"/>
+      <c r="E106" s="18"/>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="17"/>
-      <c r="B107" s="17"/>
-      <c r="C107" s="18"/>
-      <c r="D107" s="17"/>
-      <c r="E107" s="19"/>
+      <c r="A107" s="16"/>
+      <c r="B107" s="16"/>
+      <c r="C107" s="17"/>
+      <c r="D107" s="16"/>
+      <c r="E107" s="18"/>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="17"/>
-      <c r="B108" s="17"/>
-      <c r="C108" s="18"/>
-      <c r="D108" s="17"/>
-      <c r="E108" s="19"/>
+      <c r="A108" s="16"/>
+      <c r="B108" s="16"/>
+      <c r="C108" s="17"/>
+      <c r="D108" s="16"/>
+      <c r="E108" s="18"/>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="17"/>
-      <c r="B109" s="17"/>
-      <c r="C109" s="18"/>
-      <c r="D109" s="17"/>
-      <c r="E109" s="19"/>
+      <c r="A109" s="16"/>
+      <c r="B109" s="16"/>
+      <c r="C109" s="17"/>
+      <c r="D109" s="16"/>
+      <c r="E109" s="18"/>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="17"/>
-      <c r="B110" s="17"/>
-      <c r="C110" s="18"/>
-      <c r="D110" s="17"/>
-      <c r="E110" s="19"/>
+      <c r="A110" s="16"/>
+      <c r="B110" s="16"/>
+      <c r="C110" s="17"/>
+      <c r="D110" s="16"/>
+      <c r="E110" s="18"/>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="17"/>
-      <c r="B111" s="17"/>
-      <c r="C111" s="18"/>
-      <c r="D111" s="17"/>
-      <c r="E111" s="19"/>
+      <c r="A111" s="16"/>
+      <c r="B111" s="16"/>
+      <c r="C111" s="17"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="18"/>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="17"/>
-      <c r="B112" s="17"/>
-      <c r="C112" s="18"/>
-      <c r="D112" s="17"/>
-      <c r="E112" s="19"/>
+      <c r="A112" s="16"/>
+      <c r="B112" s="16"/>
+      <c r="C112" s="17"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="18"/>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="17"/>
-      <c r="B113" s="17"/>
-      <c r="C113" s="18"/>
-      <c r="D113" s="17"/>
-      <c r="E113" s="19"/>
+      <c r="A113" s="16"/>
+      <c r="B113" s="16"/>
+      <c r="C113" s="17"/>
+      <c r="D113" s="16"/>
+      <c r="E113" s="18"/>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="17"/>
-      <c r="B114" s="17"/>
-      <c r="C114" s="18"/>
-      <c r="D114" s="17"/>
-      <c r="E114" s="19"/>
+      <c r="A114" s="16"/>
+      <c r="B114" s="16"/>
+      <c r="C114" s="17"/>
+      <c r="D114" s="16"/>
+      <c r="E114" s="18"/>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="17"/>
-      <c r="B115" s="17"/>
-      <c r="C115" s="18"/>
-      <c r="D115" s="17"/>
-      <c r="E115" s="19"/>
+      <c r="A115" s="16"/>
+      <c r="B115" s="16"/>
+      <c r="C115" s="17"/>
+      <c r="D115" s="16"/>
+      <c r="E115" s="18"/>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="17"/>
-      <c r="B116" s="17"/>
-      <c r="C116" s="18"/>
-      <c r="D116" s="17"/>
-      <c r="E116" s="19"/>
+      <c r="A116" s="16"/>
+      <c r="B116" s="16"/>
+      <c r="C116" s="17"/>
+      <c r="D116" s="16"/>
+      <c r="E116" s="18"/>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="17"/>
-      <c r="B117" s="17"/>
-      <c r="C117" s="18"/>
-      <c r="D117" s="17"/>
-      <c r="E117" s="19"/>
+      <c r="A117" s="16"/>
+      <c r="B117" s="16"/>
+      <c r="C117" s="17"/>
+      <c r="D117" s="16"/>
+      <c r="E117" s="18"/>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="17"/>
-      <c r="B118" s="17"/>
-      <c r="C118" s="18"/>
-      <c r="D118" s="17"/>
-      <c r="E118" s="19"/>
+      <c r="A118" s="16"/>
+      <c r="B118" s="16"/>
+      <c r="C118" s="17"/>
+      <c r="D118" s="16"/>
+      <c r="E118" s="18"/>
     </row>
     <row r="119" spans="1:5">
-      <c r="A119" s="17"/>
-      <c r="B119" s="17"/>
-      <c r="C119" s="18"/>
-      <c r="D119" s="17"/>
-      <c r="E119" s="19"/>
+      <c r="A119" s="16"/>
+      <c r="B119" s="16"/>
+      <c r="C119" s="17"/>
+      <c r="D119" s="16"/>
+      <c r="E119" s="18"/>
     </row>
     <row r="120" spans="1:5">
-      <c r="A120" s="17"/>
-      <c r="B120" s="17"/>
-      <c r="C120" s="18"/>
-      <c r="D120" s="17"/>
-      <c r="E120" s="19"/>
+      <c r="A120" s="16"/>
+      <c r="B120" s="16"/>
+      <c r="C120" s="17"/>
+      <c r="D120" s="16"/>
+      <c r="E120" s="18"/>
     </row>
     <row r="121" spans="1:5">
-      <c r="A121" s="17"/>
-      <c r="B121" s="17"/>
-      <c r="C121" s="18"/>
-      <c r="D121" s="17"/>
-      <c r="E121" s="19"/>
+      <c r="A121" s="16"/>
+      <c r="B121" s="16"/>
+      <c r="C121" s="17"/>
+      <c r="D121" s="16"/>
+      <c r="E121" s="18"/>
     </row>
     <row r="122" spans="1:5">
-      <c r="A122" s="17"/>
-      <c r="B122" s="17"/>
-      <c r="C122" s="18"/>
-      <c r="D122" s="17"/>
-      <c r="E122" s="19"/>
+      <c r="A122" s="16"/>
+      <c r="B122" s="16"/>
+      <c r="C122" s="17"/>
+      <c r="D122" s="16"/>
+      <c r="E122" s="18"/>
     </row>
     <row r="123" spans="1:5">
-      <c r="A123" s="17"/>
-      <c r="B123" s="17"/>
-      <c r="C123" s="18"/>
-      <c r="D123" s="17"/>
-      <c r="E123" s="19"/>
+      <c r="A123" s="16"/>
+      <c r="B123" s="16"/>
+      <c r="C123" s="17"/>
+      <c r="D123" s="16"/>
+      <c r="E123" s="18"/>
     </row>
     <row r="124" spans="1:5">
-      <c r="A124" s="17"/>
-      <c r="B124" s="17"/>
-      <c r="C124" s="18"/>
-      <c r="D124" s="17"/>
-      <c r="E124" s="19"/>
+      <c r="A124" s="16"/>
+      <c r="B124" s="16"/>
+      <c r="C124" s="17"/>
+      <c r="D124" s="16"/>
+      <c r="E124" s="18"/>
     </row>
     <row r="125" spans="1:5">
-      <c r="A125" s="17"/>
-      <c r="B125" s="17"/>
-      <c r="C125" s="18"/>
-      <c r="D125" s="17"/>
-      <c r="E125" s="19"/>
+      <c r="A125" s="16"/>
+      <c r="B125" s="16"/>
+      <c r="C125" s="17"/>
+      <c r="D125" s="16"/>
+      <c r="E125" s="18"/>
     </row>
     <row r="126" spans="1:5">
-      <c r="A126" s="17"/>
-      <c r="B126" s="17"/>
-      <c r="C126" s="18"/>
-      <c r="D126" s="17"/>
-      <c r="E126" s="19"/>
+      <c r="A126" s="16"/>
+      <c r="B126" s="16"/>
+      <c r="C126" s="17"/>
+      <c r="D126" s="16"/>
+      <c r="E126" s="18"/>
     </row>
     <row r="127" spans="1:5">
-      <c r="A127" s="17"/>
-      <c r="B127" s="17"/>
-      <c r="C127" s="18"/>
-      <c r="D127" s="17"/>
-      <c r="E127" s="19"/>
+      <c r="A127" s="16"/>
+      <c r="B127" s="16"/>
+      <c r="C127" s="17"/>
+      <c r="D127" s="16"/>
+      <c r="E127" s="18"/>
     </row>
     <row r="128" spans="1:5">
-      <c r="A128" s="17"/>
-      <c r="B128" s="17"/>
-      <c r="C128" s="18"/>
-      <c r="D128" s="17"/>
-      <c r="E128" s="19"/>
+      <c r="A128" s="16"/>
+      <c r="B128" s="16"/>
+      <c r="C128" s="17"/>
+      <c r="D128" s="16"/>
+      <c r="E128" s="18"/>
     </row>
     <row r="129" spans="1:5">
-      <c r="A129" s="17"/>
-      <c r="B129" s="17"/>
-      <c r="C129" s="18"/>
-      <c r="D129" s="17"/>
-      <c r="E129" s="19"/>
+      <c r="A129" s="16"/>
+      <c r="B129" s="16"/>
+      <c r="C129" s="17"/>
+      <c r="D129" s="16"/>
+      <c r="E129" s="18"/>
     </row>
     <row r="130" spans="1:5">
-      <c r="A130" s="17"/>
-      <c r="B130" s="17"/>
-      <c r="C130" s="18"/>
-      <c r="D130" s="17"/>
-      <c r="E130" s="19"/>
+      <c r="A130" s="16"/>
+      <c r="B130" s="16"/>
+      <c r="C130" s="17"/>
+      <c r="D130" s="16"/>
+      <c r="E130" s="18"/>
     </row>
     <row r="131" spans="1:5">
-      <c r="A131" s="17"/>
-      <c r="B131" s="17"/>
-      <c r="C131" s="18"/>
-      <c r="D131" s="17"/>
-      <c r="E131" s="19"/>
+      <c r="A131" s="16"/>
+      <c r="B131" s="16"/>
+      <c r="C131" s="17"/>
+      <c r="D131" s="16"/>
+      <c r="E131" s="18"/>
     </row>
     <row r="132" spans="1:5">
-      <c r="A132" s="17"/>
-      <c r="B132" s="17"/>
-      <c r="C132" s="18"/>
-      <c r="D132" s="17"/>
-      <c r="E132" s="19"/>
+      <c r="A132" s="16"/>
+      <c r="B132" s="16"/>
+      <c r="C132" s="17"/>
+      <c r="D132" s="16"/>
+      <c r="E132" s="18"/>
     </row>
     <row r="133" spans="1:5">
-      <c r="A133" s="17"/>
-      <c r="B133" s="17"/>
-      <c r="C133" s="18"/>
-      <c r="D133" s="17"/>
-      <c r="E133" s="19"/>
+      <c r="A133" s="16"/>
+      <c r="B133" s="16"/>
+      <c r="C133" s="17"/>
+      <c r="D133" s="16"/>
+      <c r="E133" s="18"/>
     </row>
     <row r="134" spans="1:5">
-      <c r="A134" s="17"/>
-      <c r="B134" s="17"/>
-      <c r="C134" s="18"/>
-      <c r="D134" s="17"/>
-      <c r="E134" s="19"/>
+      <c r="A134" s="16"/>
+      <c r="B134" s="16"/>
+      <c r="C134" s="17"/>
+      <c r="D134" s="16"/>
+      <c r="E134" s="18"/>
     </row>
     <row r="135" spans="1:5">
-      <c r="A135" s="17"/>
-      <c r="B135" s="17"/>
-      <c r="C135" s="18"/>
-      <c r="D135" s="17"/>
-      <c r="E135" s="19"/>
+      <c r="A135" s="16"/>
+      <c r="B135" s="16"/>
+      <c r="C135" s="17"/>
+      <c r="D135" s="16"/>
+      <c r="E135" s="18"/>
     </row>
     <row r="136" spans="1:5">
-      <c r="A136" s="17"/>
-      <c r="B136" s="17"/>
-      <c r="C136" s="18"/>
-      <c r="D136" s="17"/>
-      <c r="E136" s="19"/>
+      <c r="A136" s="16"/>
+      <c r="B136" s="16"/>
+      <c r="C136" s="17"/>
+      <c r="D136" s="16"/>
+      <c r="E136" s="18"/>
     </row>
     <row r="137" spans="1:5">
-      <c r="A137" s="17"/>
-      <c r="B137" s="17"/>
-      <c r="C137" s="18"/>
-      <c r="D137" s="17"/>
-      <c r="E137" s="19"/>
+      <c r="A137" s="16"/>
+      <c r="B137" s="16"/>
+      <c r="C137" s="17"/>
+      <c r="D137" s="16"/>
+      <c r="E137" s="18"/>
     </row>
     <row r="138" spans="1:5">
-      <c r="A138" s="17"/>
-      <c r="B138" s="17"/>
-      <c r="C138" s="18"/>
-      <c r="D138" s="17"/>
-      <c r="E138" s="19"/>
+      <c r="A138" s="16"/>
+      <c r="B138" s="16"/>
+      <c r="C138" s="17"/>
+      <c r="D138" s="16"/>
+      <c r="E138" s="18"/>
     </row>
     <row r="139" spans="1:5">
-      <c r="A139" s="17"/>
-      <c r="B139" s="17"/>
-      <c r="C139" s="18"/>
-      <c r="D139" s="17"/>
-      <c r="E139" s="19"/>
+      <c r="A139" s="16"/>
+      <c r="B139" s="16"/>
+      <c r="C139" s="17"/>
+      <c r="D139" s="16"/>
+      <c r="E139" s="18"/>
     </row>
     <row r="140" spans="1:5">
-      <c r="A140" s="17"/>
-      <c r="B140" s="17"/>
-      <c r="C140" s="18"/>
-      <c r="D140" s="17"/>
-      <c r="E140" s="19"/>
+      <c r="A140" s="16"/>
+      <c r="B140" s="16"/>
+      <c r="C140" s="17"/>
+      <c r="D140" s="16"/>
+      <c r="E140" s="18"/>
     </row>
     <row r="141" spans="1:5">
-      <c r="A141" s="17"/>
-      <c r="B141" s="17"/>
-      <c r="C141" s="18"/>
-      <c r="D141" s="17"/>
-      <c r="E141" s="19"/>
+      <c r="A141" s="16"/>
+      <c r="B141" s="16"/>
+      <c r="C141" s="17"/>
+      <c r="D141" s="16"/>
+      <c r="E141" s="18"/>
     </row>
     <row r="142" spans="1:5">
-      <c r="A142" s="17"/>
-      <c r="B142" s="17"/>
-      <c r="C142" s="18"/>
-      <c r="D142" s="17"/>
-      <c r="E142" s="19"/>
+      <c r="A142" s="16"/>
+      <c r="B142" s="16"/>
+      <c r="C142" s="17"/>
+      <c r="D142" s="16"/>
+      <c r="E142" s="18"/>
     </row>
     <row r="143" spans="1:5">
-      <c r="A143" s="17"/>
-      <c r="B143" s="17"/>
-      <c r="C143" s="18"/>
-      <c r="D143" s="17"/>
-      <c r="E143" s="19"/>
+      <c r="A143" s="16"/>
+      <c r="B143" s="16"/>
+      <c r="C143" s="17"/>
+      <c r="D143" s="16"/>
+      <c r="E143" s="18"/>
     </row>
     <row r="144" spans="1:5">
-      <c r="A144" s="17"/>
-      <c r="B144" s="17"/>
-      <c r="C144" s="18"/>
-      <c r="D144" s="17"/>
-      <c r="E144" s="19"/>
+      <c r="A144" s="16"/>
+      <c r="B144" s="16"/>
+      <c r="C144" s="17"/>
+      <c r="D144" s="16"/>
+      <c r="E144" s="18"/>
     </row>
     <row r="145" spans="1:5">
-      <c r="A145" s="17"/>
-      <c r="B145" s="17"/>
-      <c r="C145" s="18"/>
-      <c r="D145" s="17"/>
-      <c r="E145" s="19"/>
+      <c r="A145" s="16"/>
+      <c r="B145" s="16"/>
+      <c r="C145" s="17"/>
+      <c r="D145" s="16"/>
+      <c r="E145" s="18"/>
     </row>
     <row r="146" spans="1:5">
-      <c r="A146" s="17"/>
-      <c r="B146" s="17"/>
-      <c r="C146" s="18"/>
-      <c r="D146" s="17"/>
-      <c r="E146" s="19"/>
+      <c r="A146" s="16"/>
+      <c r="B146" s="16"/>
+      <c r="C146" s="17"/>
+      <c r="D146" s="16"/>
+      <c r="E146" s="18"/>
     </row>
     <row r="147" spans="1:5">
-      <c r="A147" s="17"/>
-      <c r="B147" s="17"/>
-      <c r="C147" s="18"/>
-      <c r="D147" s="17"/>
-      <c r="E147" s="19"/>
+      <c r="A147" s="16"/>
+      <c r="B147" s="16"/>
+      <c r="C147" s="17"/>
+      <c r="D147" s="16"/>
+      <c r="E147" s="18"/>
     </row>
     <row r="148" spans="1:5">
-      <c r="A148" s="17"/>
-      <c r="B148" s="17"/>
-      <c r="C148" s="18"/>
-      <c r="D148" s="17"/>
-      <c r="E148" s="19"/>
+      <c r="A148" s="16"/>
+      <c r="B148" s="16"/>
+      <c r="C148" s="17"/>
+      <c r="D148" s="16"/>
+      <c r="E148" s="18"/>
     </row>
     <row r="149" spans="1:5">
-      <c r="A149" s="17"/>
-      <c r="B149" s="17"/>
-      <c r="C149" s="18"/>
-      <c r="D149" s="17"/>
-      <c r="E149" s="19"/>
+      <c r="A149" s="16"/>
+      <c r="B149" s="16"/>
+      <c r="C149" s="17"/>
+      <c r="D149" s="16"/>
+      <c r="E149" s="18"/>
     </row>
     <row r="150" spans="1:5">
-      <c r="A150" s="17"/>
-      <c r="B150" s="17"/>
-      <c r="C150" s="18"/>
-      <c r="D150" s="17"/>
-      <c r="E150" s="19"/>
+      <c r="A150" s="16"/>
+      <c r="B150" s="16"/>
+      <c r="C150" s="17"/>
+      <c r="D150" s="16"/>
+      <c r="E150" s="18"/>
     </row>
     <row r="151" spans="1:5">
-      <c r="A151" s="17"/>
-      <c r="B151" s="17"/>
-      <c r="C151" s="18"/>
-      <c r="D151" s="17"/>
-      <c r="E151" s="19"/>
+      <c r="A151" s="16"/>
+      <c r="B151" s="16"/>
+      <c r="C151" s="17"/>
+      <c r="D151" s="16"/>
+      <c r="E151" s="18"/>
     </row>
     <row r="152" spans="1:5">
-      <c r="A152" s="17"/>
-      <c r="B152" s="17"/>
-      <c r="C152" s="18"/>
-      <c r="D152" s="17"/>
-      <c r="E152" s="19"/>
+      <c r="A152" s="16"/>
+      <c r="B152" s="16"/>
+      <c r="C152" s="17"/>
+      <c r="D152" s="16"/>
+      <c r="E152" s="18"/>
     </row>
     <row r="153" spans="1:5">
-      <c r="A153" s="17"/>
-      <c r="B153" s="17"/>
-      <c r="C153" s="18"/>
-      <c r="D153" s="17"/>
-      <c r="E153" s="19"/>
+      <c r="A153" s="16"/>
+      <c r="B153" s="16"/>
+      <c r="C153" s="17"/>
+      <c r="D153" s="16"/>
+      <c r="E153" s="18"/>
     </row>
     <row r="154" spans="1:5">
-      <c r="A154" s="17"/>
-      <c r="B154" s="17"/>
-      <c r="C154" s="18"/>
-      <c r="D154" s="17"/>
-      <c r="E154" s="19"/>
+      <c r="A154" s="16"/>
+      <c r="B154" s="16"/>
+      <c r="C154" s="17"/>
+      <c r="D154" s="16"/>
+      <c r="E154" s="18"/>
     </row>
     <row r="155" spans="1:5">
-      <c r="A155" s="17"/>
-      <c r="B155" s="17"/>
-      <c r="C155" s="18"/>
-      <c r="D155" s="17"/>
-      <c r="E155" s="19"/>
+      <c r="A155" s="16"/>
+      <c r="B155" s="16"/>
+      <c r="C155" s="17"/>
+      <c r="D155" s="16"/>
+      <c r="E155" s="18"/>
     </row>
     <row r="156" spans="1:5">
-      <c r="A156" s="17"/>
-      <c r="B156" s="17"/>
-      <c r="C156" s="18"/>
-      <c r="D156" s="17"/>
-      <c r="E156" s="19"/>
+      <c r="A156" s="16"/>
+      <c r="B156" s="16"/>
+      <c r="C156" s="17"/>
+      <c r="D156" s="16"/>
+      <c r="E156" s="18"/>
     </row>
     <row r="157" spans="1:5">
-      <c r="A157" s="17"/>
-      <c r="B157" s="17"/>
-      <c r="C157" s="18"/>
-      <c r="D157" s="17"/>
-      <c r="E157" s="19"/>
+      <c r="A157" s="16"/>
+      <c r="B157" s="16"/>
+      <c r="C157" s="17"/>
+      <c r="D157" s="16"/>
+      <c r="E157" s="18"/>
     </row>
     <row r="158" spans="1:5">
-      <c r="A158" s="17"/>
-      <c r="B158" s="17"/>
-      <c r="C158" s="18"/>
-      <c r="D158" s="17"/>
-      <c r="E158" s="19"/>
+      <c r="A158" s="16"/>
+      <c r="B158" s="16"/>
+      <c r="C158" s="17"/>
+      <c r="D158" s="16"/>
+      <c r="E158" s="18"/>
     </row>
     <row r="159" spans="1:5">
-      <c r="A159" s="17"/>
-      <c r="B159" s="17"/>
-      <c r="C159" s="18"/>
-      <c r="D159" s="17"/>
-      <c r="E159" s="19"/>
+      <c r="A159" s="16"/>
+      <c r="B159" s="16"/>
+      <c r="C159" s="17"/>
+      <c r="D159" s="16"/>
+      <c r="E159" s="18"/>
     </row>
     <row r="160" spans="1:5">
-      <c r="A160" s="17"/>
-      <c r="B160" s="17"/>
-      <c r="C160" s="18"/>
-      <c r="D160" s="17"/>
-      <c r="E160" s="19"/>
+      <c r="A160" s="16"/>
+      <c r="B160" s="16"/>
+      <c r="C160" s="17"/>
+      <c r="D160" s="16"/>
+      <c r="E160" s="18"/>
     </row>
     <row r="161" spans="1:5">
-      <c r="A161" s="17"/>
-      <c r="B161" s="17"/>
-      <c r="C161" s="18"/>
-      <c r="D161" s="17"/>
-      <c r="E161" s="19"/>
+      <c r="A161" s="16"/>
+      <c r="B161" s="16"/>
+      <c r="C161" s="17"/>
+      <c r="D161" s="16"/>
+      <c r="E161" s="18"/>
     </row>
     <row r="162" spans="1:5">
-      <c r="A162" s="17"/>
-      <c r="B162" s="17"/>
-      <c r="C162" s="18"/>
-      <c r="D162" s="17"/>
-      <c r="E162" s="19"/>
+      <c r="A162" s="16"/>
+      <c r="B162" s="16"/>
+      <c r="C162" s="17"/>
+      <c r="D162" s="16"/>
+      <c r="E162" s="18"/>
     </row>
     <row r="163" spans="1:5">
-      <c r="A163" s="17"/>
-      <c r="B163" s="17"/>
-      <c r="C163" s="18"/>
-      <c r="D163" s="17"/>
-      <c r="E163" s="19"/>
+      <c r="A163" s="16"/>
+      <c r="B163" s="16"/>
+      <c r="C163" s="17"/>
+      <c r="D163" s="16"/>
+      <c r="E163" s="18"/>
     </row>
     <row r="164" spans="1:5">
-      <c r="A164" s="17"/>
-      <c r="B164" s="17"/>
-      <c r="C164" s="18"/>
-      <c r="D164" s="17"/>
-      <c r="E164" s="19"/>
+      <c r="A164" s="16"/>
+      <c r="B164" s="16"/>
+      <c r="C164" s="17"/>
+      <c r="D164" s="16"/>
+      <c r="E164" s="18"/>
     </row>
     <row r="165" spans="1:5">
-      <c r="A165" s="17"/>
-      <c r="B165" s="17"/>
-      <c r="C165" s="18"/>
-      <c r="D165" s="17"/>
-      <c r="E165" s="19"/>
+      <c r="A165" s="16"/>
+      <c r="B165" s="16"/>
+      <c r="C165" s="17"/>
+      <c r="D165" s="16"/>
+      <c r="E165" s="18"/>
     </row>
     <row r="166" spans="1:5">
-      <c r="A166" s="17"/>
-      <c r="B166" s="17"/>
-      <c r="C166" s="18"/>
-      <c r="D166" s="17"/>
-      <c r="E166" s="19"/>
+      <c r="A166" s="16"/>
+      <c r="B166" s="16"/>
+      <c r="C166" s="17"/>
+      <c r="D166" s="16"/>
+      <c r="E166" s="18"/>
     </row>
     <row r="167" spans="1:5">
-      <c r="A167" s="17"/>
-      <c r="B167" s="17"/>
-      <c r="C167" s="18"/>
-      <c r="D167" s="17"/>
-      <c r="E167" s="19"/>
+      <c r="A167" s="16"/>
+      <c r="B167" s="16"/>
+      <c r="C167" s="17"/>
+      <c r="D167" s="16"/>
+      <c r="E167" s="18"/>
     </row>
     <row r="168" spans="1:5">
-      <c r="A168" s="17"/>
-      <c r="B168" s="17"/>
-      <c r="C168" s="18"/>
-      <c r="D168" s="17"/>
-      <c r="E168" s="19"/>
+      <c r="A168" s="16"/>
+      <c r="B168" s="16"/>
+      <c r="C168" s="17"/>
+      <c r="D168" s="16"/>
+      <c r="E168" s="18"/>
     </row>
     <row r="169" spans="1:5">
-      <c r="A169" s="17"/>
-      <c r="B169" s="17"/>
-      <c r="C169" s="18"/>
-      <c r="D169" s="17"/>
-      <c r="E169" s="19"/>
+      <c r="A169" s="16"/>
+      <c r="B169" s="16"/>
+      <c r="C169" s="17"/>
+      <c r="D169" s="16"/>
+      <c r="E169" s="18"/>
     </row>
     <row r="170" spans="1:5">
-      <c r="A170" s="17"/>
-      <c r="B170" s="17"/>
-      <c r="C170" s="18"/>
-      <c r="D170" s="17"/>
-      <c r="E170" s="19"/>
+      <c r="A170" s="16"/>
+      <c r="B170" s="16"/>
+      <c r="C170" s="17"/>
+      <c r="D170" s="16"/>
+      <c r="E170" s="18"/>
     </row>
     <row r="171" spans="1:5">
-      <c r="A171" s="17"/>
-      <c r="B171" s="17"/>
-      <c r="C171" s="18"/>
-      <c r="D171" s="17"/>
-      <c r="E171" s="19"/>
+      <c r="A171" s="16"/>
+      <c r="B171" s="16"/>
+      <c r="C171" s="17"/>
+      <c r="D171" s="16"/>
+      <c r="E171" s="18"/>
     </row>
     <row r="172" spans="1:5">
-      <c r="A172" s="17"/>
-      <c r="B172" s="17"/>
-      <c r="C172" s="18"/>
-      <c r="D172" s="17"/>
-      <c r="E172" s="19"/>
+      <c r="A172" s="16"/>
+      <c r="B172" s="16"/>
+      <c r="C172" s="17"/>
+      <c r="D172" s="16"/>
+      <c r="E172" s="18"/>
     </row>
     <row r="173" spans="1:5">
-      <c r="A173" s="17"/>
-      <c r="B173" s="17"/>
-      <c r="C173" s="18"/>
-      <c r="D173" s="17"/>
-      <c r="E173" s="19"/>
+      <c r="A173" s="16"/>
+      <c r="B173" s="16"/>
+      <c r="C173" s="17"/>
+      <c r="D173" s="16"/>
+      <c r="E173" s="18"/>
     </row>
     <row r="174" spans="1:5">
-      <c r="A174" s="17"/>
-      <c r="B174" s="17"/>
-      <c r="C174" s="18"/>
-      <c r="D174" s="17"/>
-      <c r="E174" s="19"/>
+      <c r="A174" s="16"/>
+      <c r="B174" s="16"/>
+      <c r="C174" s="17"/>
+      <c r="D174" s="16"/>
+      <c r="E174" s="18"/>
     </row>
     <row r="175" spans="1:5">
-      <c r="A175" s="17"/>
-      <c r="B175" s="17"/>
-      <c r="C175" s="18"/>
-      <c r="D175" s="17"/>
-      <c r="E175" s="19"/>
+      <c r="A175" s="16"/>
+      <c r="B175" s="16"/>
+      <c r="C175" s="17"/>
+      <c r="D175" s="16"/>
+      <c r="E175" s="18"/>
     </row>
     <row r="176" spans="1:5">
-      <c r="A176" s="17"/>
-      <c r="B176" s="17"/>
-      <c r="C176" s="18"/>
-      <c r="D176" s="17"/>
-      <c r="E176" s="19"/>
+      <c r="A176" s="16"/>
+      <c r="B176" s="16"/>
+      <c r="C176" s="17"/>
+      <c r="D176" s="16"/>
+      <c r="E176" s="18"/>
     </row>
     <row r="177" spans="1:5">
-      <c r="A177" s="17"/>
-      <c r="B177" s="17"/>
-      <c r="C177" s="18"/>
-      <c r="D177" s="17"/>
-      <c r="E177" s="19"/>
-    </row>
-    <row r="178" ht="14.75" spans="1:5">
-      <c r="A178" s="17"/>
-      <c r="B178" s="17"/>
-      <c r="C178" s="18"/>
-      <c r="D178" s="17"/>
-      <c r="E178" s="19"/>
-    </row>
-    <row r="179" ht="14.75" spans="1:5">
+      <c r="A177" s="16"/>
+      <c r="B177" s="16"/>
+      <c r="C177" s="17"/>
+      <c r="D177" s="16"/>
+      <c r="E177" s="18"/>
+    </row>
+    <row r="178" ht="15" spans="1:5">
+      <c r="A178" s="16"/>
+      <c r="B178" s="16"/>
+      <c r="C178" s="17"/>
+      <c r="D178" s="16"/>
+      <c r="E178" s="18"/>
+    </row>
+    <row r="179" ht="15" spans="1:5">
       <c r="A179" s="22"/>
       <c r="B179" s="22"/>
       <c r="C179" s="22"/>
       <c r="D179" s="22"/>
       <c r="E179" s="23"/>
     </row>
-    <row r="180" ht="14.75" spans="1:5">
+    <row r="180" ht="15" spans="1:5">
       <c r="A180" s="22"/>
       <c r="B180" s="22"/>
       <c r="C180" s="22"/>
       <c r="D180" s="22"/>
       <c r="E180" s="23"/>
     </row>
-    <row r="181" ht="14.75" spans="1:5">
+    <row r="181" ht="15" spans="1:5">
       <c r="A181" s="22"/>
       <c r="B181" s="22"/>
       <c r="C181" s="22"/>

--- a/Tools/Luban/DataTables/Datas/R_任务.xlsx
+++ b/Tools/Luban/DataTables/Datas/R_任务.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17055"/>
+    <workbookView windowWidth="28800" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1746,7 +1746,7 @@
         <v>42</v>
       </c>
       <c r="J6" s="11">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="K6" s="21" t="s">
         <v>43</v>

--- a/Tools/Luban/DataTables/Datas/R_任务.xlsx
+++ b/Tools/Luban/DataTables/Datas/R_任务.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11655"/>
+    <workbookView windowHeight="18360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="121">
   <si>
     <t>##var</t>
   </si>
@@ -384,6 +384,12 @@
   </si>
   <si>
     <t>307,308</t>
+  </si>
+  <si>
+    <t>绿羊羊</t>
+  </si>
+  <si>
+    <t>白羊羊</t>
   </si>
 </sst>
 </file>
@@ -1872,7 +1878,7 @@
         <v>63</v>
       </c>
       <c r="J10" s="11">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1900,7 +1906,7 @@
         <v>68</v>
       </c>
       <c r="J11" s="11">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>69</v>
@@ -1932,9 +1938,7 @@
       <c r="I12" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="J12" s="11">
-        <v>1009</v>
-      </c>
+      <c r="J12" s="11"/>
       <c r="K12" s="1" t="s">
         <v>76</v>
       </c>
@@ -2191,10 +2195,28 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="16"/>
+      <c r="B21" s="1">
+        <v>1020</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" s="1">
+        <v>3</v>
+      </c>
       <c r="E21" s="20"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:4">
       <c r="A22" s="16"/>
+      <c r="B22" s="1">
+        <v>1021</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="16"/>
